--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G13" t="n">

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI16"/>
+  <dimension ref="A1:AI17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -618,12 +618,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -728,7 +728,7 @@
         <v>0</v>
       </c>
       <c r="AI2" s="3" t="n">
-        <v>46051.41666666666</v>
+        <v>46051.375</v>
       </c>
     </row>
     <row r="3">
@@ -737,12 +737,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -847,7 +847,7 @@
         <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
-        <v>46051.42708333334</v>
+        <v>46051.41666666666</v>
       </c>
     </row>
     <row r="4">
@@ -856,12 +856,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -966,7 +966,7 @@
         <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
-        <v>46051.47916666666</v>
+        <v>46051.42708333334</v>
       </c>
     </row>
     <row r="5">
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1085,7 +1085,7 @@
         <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
-        <v>46051.5</v>
+        <v>46051.47916666666</v>
       </c>
     </row>
     <row r="6">
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1323,7 +1323,7 @@
         <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
-        <v>46051.52083333334</v>
+        <v>46051.5</v>
       </c>
     </row>
     <row r="8">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1442,7 +1442,7 @@
         <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>46051.54166666666</v>
+        <v>46051.52083333334</v>
       </c>
     </row>
     <row r="9">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1561,7 +1561,7 @@
         <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>46051.5625</v>
+        <v>46051.54166666666</v>
       </c>
     </row>
     <row r="10">
@@ -1570,12 +1570,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1680,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>46051.60416666666</v>
+        <v>46051.5625</v>
       </c>
     </row>
     <row r="11">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1918,7 +1918,7 @@
         <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>46051.625</v>
+        <v>46051.60416666666</v>
       </c>
     </row>
     <row r="13">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2083,80 +2083,80 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>46051.70833333334</v>
+        <v>46051.625</v>
       </c>
     </row>
     <row r="15">
@@ -2165,27 +2165,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2202,80 +2202,80 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.74</v>
+        <v>4.6</v>
       </c>
       <c r="M15" t="n">
-        <v>3.64</v>
+        <v>3.5</v>
       </c>
       <c r="N15" t="n">
-        <v>4.65</v>
+        <v>1.73</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB15" t="n">
         <v>1.75</v>
       </c>
-      <c r="AB15" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>46051.83333333334</v>
+        <v>46051.70833333334</v>
       </c>
     </row>
     <row r="16">
@@ -2284,116 +2284,235 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="N16" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" s="3" t="n">
+        <v>46051.83333333334</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Brazil Serie A</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Botafogo</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Cruzeiro</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="inlineStr">
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L16" t="n">
+      <c r="L17" t="n">
         <v>2.13</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M17" t="n">
         <v>3.05</v>
       </c>
-      <c r="N16" t="n">
+      <c r="N17" t="n">
         <v>3.5</v>
       </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
         <v>2.1</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AB17" t="n">
         <v>1.67</v>
       </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" s="3" t="n">
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" s="3" t="n">
         <v>46051.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G12" t="n">

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="M16" t="n">
-        <v>3.64</v>
+        <v>3.58</v>
       </c>
       <c r="N16" t="n">
-        <v>4.65</v>
+        <v>4.2</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AB16" t="n">
         <v>2.05</v>

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1067,10 +1067,10 @@
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1293,10 +1293,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2007,10 +2007,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2126,10 +2126,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="M17" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1174,10 +1174,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1293,10 +1293,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.85</v>
+        <v>1.83</v>
       </c>
       <c r="M13" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="N13" t="n">
-        <v>3.35</v>
+        <v>5.3</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2007,10 +2007,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.83</v>
+        <v>2.85</v>
       </c>
       <c r="M14" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="N14" t="n">
-        <v>5.3</v>
+        <v>3.35</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2126,10 +2126,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.13</v>
+        <v>2.02</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1174,10 +1174,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1293,10 +1293,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.83</v>
+        <v>2.85</v>
       </c>
       <c r="M13" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="N13" t="n">
-        <v>5.3</v>
+        <v>3.35</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2007,10 +2007,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.13</v>
+        <v>2.02</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.85</v>
+        <v>1.83</v>
       </c>
       <c r="M14" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="N14" t="n">
-        <v>3.35</v>
+        <v>5.3</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2126,10 +2126,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.85</v>
+        <v>1.83</v>
       </c>
       <c r="M13" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="N13" t="n">
-        <v>3.35</v>
+        <v>5.3</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2007,10 +2007,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.83</v>
+        <v>2.85</v>
       </c>
       <c r="M14" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="N14" t="n">
-        <v>5.3</v>
+        <v>3.35</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2126,10 +2126,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.13</v>
+        <v>2.02</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.83</v>
+        <v>2.85</v>
       </c>
       <c r="M13" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="N13" t="n">
-        <v>5.3</v>
+        <v>3.35</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2007,10 +2007,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.13</v>
+        <v>2.02</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.85</v>
+        <v>1.83</v>
       </c>
       <c r="M14" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="N14" t="n">
-        <v>3.35</v>
+        <v>5.3</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2126,10 +2126,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1174,10 +1174,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1293,10 +1293,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.85</v>
+        <v>1.83</v>
       </c>
       <c r="M13" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="N13" t="n">
-        <v>3.35</v>
+        <v>5.3</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2007,10 +2007,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.83</v>
+        <v>2.85</v>
       </c>
       <c r="M14" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="N14" t="n">
-        <v>5.3</v>
+        <v>3.35</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2126,10 +2126,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.13</v>
+        <v>2.02</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.83</v>
+        <v>2.85</v>
       </c>
       <c r="M13" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="N13" t="n">
-        <v>5.3</v>
+        <v>3.35</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2007,10 +2007,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.13</v>
+        <v>2.02</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.85</v>
+        <v>1.83</v>
       </c>
       <c r="M14" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="N14" t="n">
-        <v>3.35</v>
+        <v>5.3</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2126,10 +2126,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1174,10 +1174,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1293,10 +1293,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.85</v>
+        <v>1.83</v>
       </c>
       <c r="M13" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="N13" t="n">
-        <v>3.35</v>
+        <v>5.3</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2007,10 +2007,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.83</v>
+        <v>2.85</v>
       </c>
       <c r="M14" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="N14" t="n">
-        <v>5.3</v>
+        <v>3.35</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2126,10 +2126,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.13</v>
+        <v>2.02</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1174,10 +1174,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1293,10 +1293,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.83</v>
+        <v>2.85</v>
       </c>
       <c r="M13" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="N13" t="n">
-        <v>5.3</v>
+        <v>3.35</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2007,10 +2007,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.13</v>
+        <v>2.02</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.85</v>
+        <v>1.83</v>
       </c>
       <c r="M14" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="N14" t="n">
-        <v>3.35</v>
+        <v>5.3</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2126,10 +2126,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1174,10 +1174,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1293,10 +1293,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2</v>
+        <v>2.85</v>
       </c>
       <c r="N17" t="n">
-        <v>3.3</v>
+        <v>2.79</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1293,10 +1293,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1293,10 +1293,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.85</v>
+        <v>1.83</v>
       </c>
       <c r="M13" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="N13" t="n">
-        <v>3.35</v>
+        <v>5.3</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2007,10 +2007,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.83</v>
+        <v>2.85</v>
       </c>
       <c r="M14" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="N14" t="n">
-        <v>5.3</v>
+        <v>3.35</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2126,10 +2126,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.13</v>
+        <v>2.02</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1174,10 +1174,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1293,10 +1293,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.83</v>
+        <v>2.85</v>
       </c>
       <c r="M13" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="N13" t="n">
-        <v>5.3</v>
+        <v>3.35</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2007,10 +2007,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.13</v>
+        <v>2.02</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.85</v>
+        <v>1.83</v>
       </c>
       <c r="M14" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="N14" t="n">
-        <v>3.35</v>
+        <v>5.3</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2126,10 +2126,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1174,10 +1174,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G7" t="n">

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.85</v>
+        <v>1.83</v>
       </c>
       <c r="M13" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="N13" t="n">
-        <v>3.35</v>
+        <v>5.3</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2007,10 +2007,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.83</v>
+        <v>2.85</v>
       </c>
       <c r="M14" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="N14" t="n">
-        <v>5.3</v>
+        <v>3.35</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2126,10 +2126,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.13</v>
+        <v>2.02</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1293,10 +1293,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="M13" t="n">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="N13" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.85</v>
+        <v>2.46</v>
       </c>
       <c r="M14" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="N14" t="n">
-        <v>3.35</v>
+        <v>3.47</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI17"/>
+  <dimension ref="A1:AI18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1174,10 +1174,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1293,10 +1293,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -2165,12 +2165,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2202,80 +2202,80 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>46051.70833333334</v>
+        <v>46051.625</v>
       </c>
     </row>
     <row r="16">
@@ -2284,27 +2284,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2321,80 +2321,80 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.66</v>
+        <v>4.6</v>
       </c>
       <c r="M16" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="N16" t="n">
-        <v>4.2</v>
+        <v>1.73</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>46051.83333333334</v>
+        <v>46051.70833333334</v>
       </c>
     </row>
     <row r="17">
@@ -2403,116 +2403,235 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="N17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" s="3" t="n">
+        <v>46051.83333333334</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Brazil Serie A</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Botafogo</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Cruzeiro</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="inlineStr">
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L17" t="n">
+      <c r="L18" t="n">
         <v>2.44</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M18" t="n">
         <v>2.85</v>
       </c>
-      <c r="N17" t="n">
+      <c r="N18" t="n">
         <v>2.79</v>
       </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
         <v>1.86</v>
       </c>
-      <c r="AB17" t="n">
+      <c r="AB18" t="n">
         <v>1.84</v>
       </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" s="3" t="n">
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" s="3" t="n">
         <v>46051.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.74</v>
+        <v>2.46</v>
       </c>
       <c r="M13" t="n">
-        <v>2.87</v>
+        <v>2.36</v>
       </c>
       <c r="N13" t="n">
-        <v>5.1</v>
+        <v>3.47</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2007,10 +2007,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.13</v>
+        <v>2.02</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2126,10 +2126,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2245,10 +2245,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1174,10 +1174,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1293,10 +1293,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1174,10 +1174,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.99</v>
+        <v>6.5</v>
       </c>
       <c r="M7" t="n">
-        <v>2.47</v>
+        <v>5</v>
       </c>
       <c r="N7" t="n">
-        <v>2.63</v>
+        <v>1.38</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>5.64</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.7</v>
+        <v>1.09</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.02</v>
+        <v>6.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46051.5</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2007,10 +2007,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2126,10 +2126,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.99</v>
+        <v>6.5</v>
       </c>
       <c r="M6" t="n">
-        <v>2.47</v>
+        <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>2.63</v>
+        <v>1.38</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>5.64</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.7</v>
+        <v>1.09</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.02</v>
+        <v>6.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46051.5</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>6.5</v>
+        <v>2.99</v>
       </c>
       <c r="M7" t="n">
-        <v>5</v>
+        <v>2.47</v>
       </c>
       <c r="N7" t="n">
-        <v>1.38</v>
+        <v>2.63</v>
       </c>
       <c r="O7" t="n">
-        <v>5.64</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.09</v>
+        <v>1.7</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.5</v>
+        <v>2.02</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46051.5</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2007,10 +2007,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2245,10 +2245,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -665,7 +665,7 @@
         <v>2.72</v>
       </c>
       <c r="N2" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -1138,19 +1138,19 @@
         <v>6.5</v>
       </c>
       <c r="M6" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="N6" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="O6" t="n">
-        <v>5.64</v>
+        <v>5.75</v>
       </c>
       <c r="P6" t="n">
         <v>2.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
@@ -1159,7 +1159,7 @@
         <v>3.9</v>
       </c>
       <c r="T6" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="U6" t="n">
         <v>1.71</v>
@@ -1174,31 +1174,31 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AB6" t="n">
         <v>2.9</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AD6" t="n">
         <v>1.76</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AH6" t="n">
         <v>1.06</v>
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.99</v>
+        <v>3.02</v>
       </c>
       <c r="M7" t="n">
-        <v>2.47</v>
+        <v>2.62</v>
       </c>
       <c r="N7" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46051.5</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46051.60416666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46051.60416666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.74</v>
+        <v>2.54</v>
       </c>
       <c r="M13" t="n">
-        <v>2.87</v>
+        <v>2.4</v>
       </c>
       <c r="N13" t="n">
-        <v>5.1</v>
+        <v>3.63</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46051.625</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.46</v>
+        <v>1.74</v>
       </c>
       <c r="M14" t="n">
-        <v>2.36</v>
+        <v>2.87</v>
       </c>
       <c r="N14" t="n">
-        <v>3.47</v>
+        <v>5.1</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>6.26</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.02</v>
+        <v>2.19</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46051.625</v>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L16" t="n">

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="M5" t="n">
-        <v>4.2</v>
+        <v>4.29</v>
       </c>
       <c r="N5" t="n">
         <v>1.55</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46051.47916666666</v>
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="M10" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.9</v>
+        <v>2.11</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46051.5625</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46051.625</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46051.625</v>
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="M16" t="n">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="N16" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="O16" t="n">
         <v>5.23</v>
@@ -2349,10 +2349,10 @@
         <v>2.52</v>
       </c>
       <c r="T16" t="n">
-        <v>2.96</v>
+        <v>2.99</v>
       </c>
       <c r="U16" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V16" t="n">
         <v>7.5</v>
@@ -2370,10 +2370,10 @@
         <v>2.97</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AC16" t="n">
         <v>3.5</v>

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="V6" t="n">
+        <v>15</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC6" t="n">
         <v>6.5</v>
       </c>
-      <c r="M6" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="O6" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2</v>
-      </c>
       <c r="AD6" t="n">
-        <v>1.76</v>
+        <v>1.04</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.5</v>
+        <v>2.45</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.38</v>
+        <v>1.46</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.11</v>
+        <v>1.41</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.06</v>
+        <v>1.36</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46051.5</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.02</v>
+        <v>6.5</v>
       </c>
       <c r="M7" t="n">
-        <v>2.62</v>
+        <v>4.75</v>
       </c>
       <c r="N7" t="n">
-        <v>2.5</v>
+        <v>1.37</v>
       </c>
       <c r="O7" t="n">
-        <v>4.2</v>
+        <v>5.75</v>
       </c>
       <c r="P7" t="n">
-        <v>1.64</v>
+        <v>2.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.72</v>
+        <v>1.83</v>
       </c>
       <c r="R7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD7" t="n">
         <v>1.76</v>
       </c>
-      <c r="S7" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="T7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="V7" t="n">
-        <v>15</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AE7" t="n">
-        <v>2.45</v>
+        <v>1.5</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.46</v>
+        <v>2.38</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.41</v>
+        <v>1.11</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.36</v>
+        <v>1.06</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46051.5</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46051.625</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.26</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46051.625</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.54</v>
+        <v>1.74</v>
       </c>
       <c r="M15" t="n">
-        <v>2.4</v>
+        <v>2.87</v>
       </c>
       <c r="N15" t="n">
-        <v>3.63</v>
+        <v>5.1</v>
       </c>
       <c r="O15" t="n">
-        <v>3.46</v>
+        <v>2.57</v>
       </c>
       <c r="P15" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.85</v>
+        <v>6.26</v>
       </c>
       <c r="R15" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="S15" t="n">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="T15" t="n">
-        <v>4.5</v>
+        <v>3.86</v>
       </c>
       <c r="U15" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="V15" t="n">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.2</v>
+        <v>2.74</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="AC15" t="n">
-        <v>6.5</v>
+        <v>5.45</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AF15" t="n">
         <v>1.48</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.46</v>
+        <v>1.11</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.42</v>
+        <v>1.82</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46051.625</v>

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="M11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z11" t="n">
         <v>3.7</v>
       </c>
-      <c r="N11" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="O11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V11" t="n">
-        <v>5</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4.7</v>
-      </c>
       <c r="AA11" t="n">
-        <v>1.49</v>
+        <v>1.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.3</v>
+        <v>1.86</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.32</v>
+        <v>3.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.54</v>
+        <v>1.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.47</v>
+        <v>1.66</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.47</v>
+        <v>2.14</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.74</v>
+        <v>1.26</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46051.60416666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M12" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="N12" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="O12" t="n">
-        <v>3.78</v>
+        <v>3.6</v>
       </c>
       <c r="P12" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.83</v>
+        <v>2.43</v>
       </c>
       <c r="R12" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>2.78</v>
+        <v>3.34</v>
       </c>
       <c r="T12" t="n">
-        <v>2.7</v>
+        <v>2.27</v>
       </c>
       <c r="U12" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="V12" t="n">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.9</v>
+        <v>1.49</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.86</v>
+        <v>2.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.2</v>
+        <v>2.32</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.3</v>
+        <v>1.54</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.66</v>
+        <v>1.47</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.14</v>
+        <v>2.47</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.26</v>
+        <v>1.74</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46051.60416666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46051.625</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46051.625</v>
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="M17" t="n">
-        <v>3.58</v>
+        <v>3.62</v>
       </c>
       <c r="N17" t="n">
-        <v>4.2</v>
+        <v>4.09</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="AB17" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF17" t="n">
         <v>2.05</v>
       </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0</v>
-      </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46051.83333333334</v>
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="M18" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="N18" t="n">
         <v>2.85</v>
       </c>
-      <c r="N18" t="n">
-        <v>2.79</v>
-      </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AB18" t="n">
         <v>1.84</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46051.89583333334</v>

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -1016,19 +1016,19 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.33</v>
+        <v>4.41</v>
       </c>
       <c r="M5" t="n">
-        <v>4.29</v>
+        <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="O5" t="n">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="P5" t="n">
-        <v>2.51</v>
+        <v>2.73</v>
       </c>
       <c r="Q5" t="n">
         <v>2</v>
@@ -1040,13 +1040,13 @@
         <v>4</v>
       </c>
       <c r="T5" t="n">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="U5" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="V5" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="W5" t="n">
         <v>1.15</v>
@@ -1055,16 +1055,16 @@
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.75</v>
+        <v>5.97</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="AC5" t="n">
         <v>1.94</v>
@@ -1073,10 +1073,10 @@
         <v>1.77</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="AG5" t="n">
         <v>1.14</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.02</v>
+        <v>6.31</v>
       </c>
       <c r="M6" t="n">
-        <v>2.62</v>
+        <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>2.5</v>
+        <v>1.36</v>
       </c>
       <c r="O6" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="P6" t="n">
-        <v>1.64</v>
+        <v>2.57</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.72</v>
+        <v>1.8</v>
       </c>
       <c r="R6" t="n">
-        <v>1.76</v>
+        <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>1.94</v>
+        <v>3.84</v>
       </c>
       <c r="T6" t="n">
-        <v>4.2</v>
+        <v>2.01</v>
       </c>
       <c r="U6" t="n">
-        <v>1.13</v>
+        <v>1.71</v>
       </c>
       <c r="V6" t="n">
-        <v>15</v>
+        <v>4.15</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.16</v>
       </c>
       <c r="X6" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.72</v>
+        <v>1.11</v>
       </c>
       <c r="Z6" t="n">
-        <v>2</v>
+        <v>6.25</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.33</v>
+        <v>2.74</v>
       </c>
       <c r="AC6" t="n">
-        <v>6.5</v>
+        <v>1.95</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.04</v>
+        <v>1.79</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.45</v>
+        <v>1.52</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.46</v>
+        <v>2.34</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.41</v>
+        <v>2.66</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.36</v>
+        <v>1.06</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46051.5</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>6.5</v>
+        <v>2.87</v>
       </c>
       <c r="M7" t="n">
-        <v>4.75</v>
+        <v>2.62</v>
       </c>
       <c r="N7" t="n">
-        <v>1.37</v>
+        <v>2.5</v>
       </c>
       <c r="O7" t="n">
-        <v>5.75</v>
+        <v>4.2</v>
       </c>
       <c r="P7" t="n">
-        <v>2.6</v>
+        <v>1.64</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.83</v>
+        <v>3.74</v>
       </c>
       <c r="R7" t="n">
-        <v>1.18</v>
+        <v>1.76</v>
       </c>
       <c r="S7" t="n">
-        <v>3.9</v>
+        <v>1.94</v>
       </c>
       <c r="T7" t="n">
-        <v>2.01</v>
+        <v>4.5</v>
       </c>
       <c r="U7" t="n">
-        <v>1.71</v>
+        <v>1.13</v>
       </c>
       <c r="V7" t="n">
-        <v>4.1</v>
+        <v>15</v>
       </c>
       <c r="W7" t="n">
-        <v>1.16</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.07</v>
+        <v>1.76</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.9</v>
+        <v>2.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.9</v>
+        <v>1.26</v>
       </c>
       <c r="AC7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.76</v>
+        <v>1.04</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.5</v>
+        <v>2.45</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.38</v>
+        <v>1.48</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.11</v>
+        <v>1.41</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.06</v>
+        <v>1.33</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46051.5</v>
@@ -1611,61 +1611,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="M10" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="N10" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="O10" t="n">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="P10" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="Q10" t="n">
         <v>4.84</v>
       </c>
       <c r="R10" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S10" t="n">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="T10" t="n">
-        <v>2.46</v>
+        <v>2.41</v>
       </c>
       <c r="U10" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="V10" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="W10" t="n">
         <v>1.07</v>
       </c>
       <c r="X10" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
         <v>1.16</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE10" t="n">
         <v>1.63</v>
@@ -1674,10 +1674,10 @@
         <v>2.12</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46051.5625</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="N11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="T11" t="n">
         <v>2.2</v>
       </c>
-      <c r="O11" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.7</v>
-      </c>
       <c r="U11" t="n">
-        <v>1.38</v>
+        <v>1.63</v>
       </c>
       <c r="V11" t="n">
-        <v>6.6</v>
+        <v>4.55</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.7</v>
+        <v>5.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.86</v>
+        <v>2.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.2</v>
+        <v>2.12</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.3</v>
+        <v>1.64</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.66</v>
+        <v>1.41</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.14</v>
+        <v>2.55</v>
       </c>
       <c r="AG11" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.26</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.3</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46051.60416666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.12</v>
+        <v>3.01</v>
       </c>
       <c r="M12" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="N12" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="O12" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P12" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.43</v>
+        <v>2.83</v>
       </c>
       <c r="R12" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="S12" t="n">
-        <v>3.34</v>
+        <v>2.95</v>
       </c>
       <c r="T12" t="n">
-        <v>2.27</v>
+        <v>2.7</v>
       </c>
       <c r="U12" t="n">
-        <v>1.56</v>
+        <v>1.38</v>
       </c>
       <c r="V12" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="W12" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X12" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.7</v>
+        <v>3.42</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.49</v>
+        <v>1.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.32</v>
+        <v>3.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.54</v>
+        <v>1.33</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.47</v>
+        <v>1.67</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.47</v>
+        <v>2.05</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.74</v>
+        <v>1.26</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46051.60416666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46051.625</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.54</v>
+        <v>1.9</v>
       </c>
       <c r="M14" t="n">
-        <v>2.4</v>
+        <v>3.46</v>
       </c>
       <c r="N14" t="n">
-        <v>3.63</v>
+        <v>3.5</v>
       </c>
       <c r="O14" t="n">
-        <v>3.46</v>
+        <v>2.5</v>
       </c>
       <c r="P14" t="n">
-        <v>1.76</v>
+        <v>2.12</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.85</v>
+        <v>4.39</v>
       </c>
       <c r="R14" t="n">
-        <v>1.83</v>
+        <v>1.36</v>
       </c>
       <c r="S14" t="n">
-        <v>1.87</v>
+        <v>2.85</v>
       </c>
       <c r="T14" t="n">
-        <v>4.5</v>
+        <v>2.73</v>
       </c>
       <c r="U14" t="n">
-        <v>1.13</v>
+        <v>1.39</v>
       </c>
       <c r="V14" t="n">
-        <v>15</v>
+        <v>6.6</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE14" t="n">
         <v>1.72</v>
       </c>
-      <c r="Z14" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AF14" t="n">
-        <v>1.48</v>
+        <v>2.01</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.46</v>
+        <v>1.26</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.42</v>
+        <v>1.81</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46051.625</v>
@@ -2215,61 +2215,61 @@
         <v>5.1</v>
       </c>
       <c r="O15" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="P15" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.26</v>
+        <v>5.25</v>
       </c>
       <c r="R15" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="S15" t="n">
         <v>2.1</v>
       </c>
       <c r="T15" t="n">
-        <v>3.86</v>
+        <v>3.8</v>
       </c>
       <c r="U15" t="n">
         <v>1.18</v>
       </c>
       <c r="V15" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="W15" t="n">
         <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AA15" t="n">
         <v>2.74</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>5.45</v>
+        <v>5.94</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AF15" t="n">
         <v>1.48</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.11</v>
+        <v>1.31</v>
       </c>
       <c r="AH15" t="n">
         <v>1.82</v>

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>6.31</v>
+        <v>2.87</v>
       </c>
       <c r="M6" t="n">
-        <v>5</v>
+        <v>2.62</v>
       </c>
       <c r="N6" t="n">
-        <v>1.36</v>
+        <v>2.5</v>
       </c>
       <c r="O6" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="P6" t="n">
-        <v>2.57</v>
+        <v>1.64</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.8</v>
+        <v>3.74</v>
       </c>
       <c r="R6" t="n">
-        <v>1.18</v>
+        <v>1.76</v>
       </c>
       <c r="S6" t="n">
-        <v>3.84</v>
+        <v>1.94</v>
       </c>
       <c r="T6" t="n">
-        <v>2.01</v>
+        <v>4.5</v>
       </c>
       <c r="U6" t="n">
-        <v>1.71</v>
+        <v>1.13</v>
       </c>
       <c r="V6" t="n">
-        <v>4.15</v>
+        <v>15</v>
       </c>
       <c r="W6" t="n">
-        <v>1.16</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.11</v>
+        <v>1.76</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.25</v>
+        <v>2.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.74</v>
+        <v>1.26</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.95</v>
+        <v>7</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.79</v>
+        <v>1.04</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.52</v>
+        <v>2.45</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.34</v>
+        <v>1.48</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.66</v>
+        <v>1.41</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.06</v>
+        <v>1.33</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46051.5</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.87</v>
+        <v>6.31</v>
       </c>
       <c r="M7" t="n">
-        <v>2.62</v>
+        <v>5</v>
       </c>
       <c r="N7" t="n">
-        <v>2.5</v>
+        <v>1.36</v>
       </c>
       <c r="O7" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="P7" t="n">
-        <v>1.64</v>
+        <v>2.57</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.74</v>
+        <v>1.8</v>
       </c>
       <c r="R7" t="n">
-        <v>1.76</v>
+        <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.94</v>
+        <v>3.84</v>
       </c>
       <c r="T7" t="n">
-        <v>4.5</v>
+        <v>2.01</v>
       </c>
       <c r="U7" t="n">
-        <v>1.13</v>
+        <v>1.71</v>
       </c>
       <c r="V7" t="n">
-        <v>15</v>
+        <v>4.15</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>1.16</v>
       </c>
       <c r="X7" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.76</v>
+        <v>1.11</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.1</v>
+        <v>6.25</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.26</v>
+        <v>2.74</v>
       </c>
       <c r="AC7" t="n">
-        <v>7</v>
+        <v>1.95</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.04</v>
+        <v>1.79</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.45</v>
+        <v>1.52</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.48</v>
+        <v>2.34</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.41</v>
+        <v>2.66</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.33</v>
+        <v>1.06</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46051.5</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.4</v>
+        <v>3.01</v>
       </c>
       <c r="M11" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="N11" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="O11" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P11" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.42</v>
+        <v>2.83</v>
       </c>
       <c r="R11" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="S11" t="n">
-        <v>3.58</v>
+        <v>2.95</v>
       </c>
       <c r="T11" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="U11" t="n">
-        <v>1.63</v>
+        <v>1.38</v>
       </c>
       <c r="V11" t="n">
-        <v>4.55</v>
+        <v>6.6</v>
       </c>
       <c r="W11" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.25</v>
+        <v>3.42</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.12</v>
+        <v>3.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.64</v>
+        <v>1.33</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.41</v>
+        <v>1.67</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.72</v>
+        <v>1.26</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46051.60416666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.01</v>
+        <v>3.4</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="N12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="T12" t="n">
         <v>2.2</v>
       </c>
-      <c r="O12" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.7</v>
-      </c>
       <c r="U12" t="n">
-        <v>1.38</v>
+        <v>1.63</v>
       </c>
       <c r="V12" t="n">
-        <v>6.6</v>
+        <v>4.55</v>
       </c>
       <c r="W12" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.3</v>
+        <v>1.09</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.42</v>
+        <v>5.25</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.2</v>
+        <v>2.12</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.33</v>
+        <v>1.64</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.67</v>
+        <v>1.41</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.05</v>
+        <v>2.55</v>
       </c>
       <c r="AG12" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AH12" t="n">
         <v>1.26</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.3</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46051.60416666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.9</v>
+        <v>1.74</v>
       </c>
       <c r="M14" t="n">
-        <v>3.46</v>
+        <v>2.87</v>
       </c>
       <c r="N14" t="n">
-        <v>3.5</v>
+        <v>5.1</v>
       </c>
       <c r="O14" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V14" t="n">
+        <v>13</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AE14" t="n">
         <v>2.5</v>
       </c>
-      <c r="P14" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V14" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AF14" t="n">
-        <v>2.01</v>
+        <v>1.48</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46051.625</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.74</v>
+        <v>1.9</v>
       </c>
       <c r="M15" t="n">
-        <v>2.87</v>
+        <v>3.46</v>
       </c>
       <c r="N15" t="n">
-        <v>5.1</v>
+        <v>3.5</v>
       </c>
       <c r="O15" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="P15" t="n">
-        <v>1.85</v>
+        <v>2.12</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.25</v>
+        <v>4.39</v>
       </c>
       <c r="R15" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>2.1</v>
+        <v>2.85</v>
       </c>
       <c r="T15" t="n">
-        <v>3.8</v>
+        <v>2.73</v>
       </c>
       <c r="U15" t="n">
-        <v>1.18</v>
+        <v>1.39</v>
       </c>
       <c r="V15" t="n">
-        <v>13</v>
+        <v>6.6</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X15" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.62</v>
+        <v>1.24</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.2</v>
+        <v>3.34</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.74</v>
+        <v>1.88</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.4</v>
+        <v>1.88</v>
       </c>
       <c r="AC15" t="n">
-        <v>5.94</v>
+        <v>3.35</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.5</v>
+        <v>1.72</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.48</v>
+        <v>2.01</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46051.625</v>

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.87</v>
+        <v>6.31</v>
       </c>
       <c r="M6" t="n">
-        <v>2.62</v>
+        <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>2.5</v>
+        <v>1.36</v>
       </c>
       <c r="O6" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="P6" t="n">
-        <v>1.64</v>
+        <v>2.57</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.74</v>
+        <v>1.8</v>
       </c>
       <c r="R6" t="n">
-        <v>1.76</v>
+        <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>1.94</v>
+        <v>3.84</v>
       </c>
       <c r="T6" t="n">
-        <v>4.5</v>
+        <v>2.01</v>
       </c>
       <c r="U6" t="n">
-        <v>1.13</v>
+        <v>1.71</v>
       </c>
       <c r="V6" t="n">
-        <v>15</v>
+        <v>4.15</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.16</v>
       </c>
       <c r="X6" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.76</v>
+        <v>1.11</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.1</v>
+        <v>6.25</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.26</v>
+        <v>2.74</v>
       </c>
       <c r="AC6" t="n">
-        <v>7</v>
+        <v>1.95</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.04</v>
+        <v>1.79</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.45</v>
+        <v>1.52</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.48</v>
+        <v>2.34</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.41</v>
+        <v>2.66</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.33</v>
+        <v>1.06</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46051.5</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>6.31</v>
+        <v>2.87</v>
       </c>
       <c r="M7" t="n">
-        <v>5</v>
+        <v>2.62</v>
       </c>
       <c r="N7" t="n">
-        <v>1.36</v>
+        <v>2.5</v>
       </c>
       <c r="O7" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="P7" t="n">
-        <v>2.57</v>
+        <v>1.64</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.8</v>
+        <v>3.74</v>
       </c>
       <c r="R7" t="n">
-        <v>1.18</v>
+        <v>1.76</v>
       </c>
       <c r="S7" t="n">
-        <v>3.84</v>
+        <v>1.94</v>
       </c>
       <c r="T7" t="n">
-        <v>2.01</v>
+        <v>4.5</v>
       </c>
       <c r="U7" t="n">
-        <v>1.71</v>
+        <v>1.13</v>
       </c>
       <c r="V7" t="n">
-        <v>4.15</v>
+        <v>15</v>
       </c>
       <c r="W7" t="n">
-        <v>1.16</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.11</v>
+        <v>1.76</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.25</v>
+        <v>2.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.74</v>
+        <v>1.26</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.95</v>
+        <v>7</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.79</v>
+        <v>1.04</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.52</v>
+        <v>2.45</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.34</v>
+        <v>1.48</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.66</v>
+        <v>1.41</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.06</v>
+        <v>1.33</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46051.5</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,61 +1968,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.5</v>
+        <v>1.74</v>
       </c>
       <c r="M13" t="n">
-        <v>2.45</v>
+        <v>2.87</v>
       </c>
       <c r="N13" t="n">
-        <v>3.2</v>
+        <v>5.1</v>
       </c>
       <c r="O13" t="n">
-        <v>3.62</v>
+        <v>2.55</v>
       </c>
       <c r="P13" t="n">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="Q13" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="R13" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="S13" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="T13" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="U13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V13" t="n">
+        <v>13</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X13" t="n">
         <v>1.13</v>
       </c>
-      <c r="V13" t="n">
-        <v>15</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.18</v>
-      </c>
       <c r="Y13" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="Z13" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.1</v>
+        <v>2.74</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AC13" t="n">
-        <v>6.7</v>
+        <v>5.94</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AE13" t="n">
         <v>2.5</v>
@@ -2031,10 +2031,10 @@
         <v>1.48</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.44</v>
+        <v>1.82</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46051.625</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.74</v>
+        <v>2.05</v>
       </c>
       <c r="M14" t="n">
-        <v>2.87</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>5.1</v>
+        <v>3.2</v>
       </c>
       <c r="O14" t="n">
-        <v>2.55</v>
+        <v>2.73</v>
       </c>
       <c r="P14" t="n">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.25</v>
+        <v>4.03</v>
       </c>
       <c r="R14" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1</v>
+        <v>2.77</v>
       </c>
       <c r="T14" t="n">
-        <v>3.8</v>
+        <v>2.77</v>
       </c>
       <c r="U14" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="V14" t="n">
-        <v>13</v>
+        <v>6.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.2</v>
+        <v>3.28</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.74</v>
+        <v>1.93</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.4</v>
+        <v>1.86</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.94</v>
+        <v>3.35</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.5</v>
+        <v>1.71</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.48</v>
+        <v>2.02</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.82</v>
+        <v>1.66</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46051.625</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="M15" t="n">
-        <v>3.46</v>
+        <v>2.45</v>
       </c>
       <c r="N15" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="O15" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>4</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="V15" t="n">
+        <v>15</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AE15" t="n">
         <v>2.5</v>
       </c>
-      <c r="P15" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V15" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AF15" t="n">
-        <v>2.01</v>
+        <v>1.48</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.81</v>
+        <v>1.44</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46051.625</v>

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>6.31</v>
+        <v>7</v>
       </c>
       <c r="M6" t="n">
         <v>5</v>
@@ -1144,7 +1144,7 @@
         <v>1.36</v>
       </c>
       <c r="O6" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="P6" t="n">
         <v>2.57</v>
@@ -1198,7 +1198,7 @@
         <v>2.34</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.66</v>
+        <v>1.14</v>
       </c>
       <c r="AH6" t="n">
         <v>1.06</v>
@@ -1736,7 +1736,7 @@
         <v>3.2</v>
       </c>
       <c r="N11" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O11" t="n">
         <v>3.65</v>
@@ -1748,10 +1748,10 @@
         <v>2.83</v>
       </c>
       <c r="R11" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="S11" t="n">
-        <v>2.95</v>
+        <v>2.77</v>
       </c>
       <c r="T11" t="n">
         <v>2.7</v>
@@ -1763,7 +1763,7 @@
         <v>6.6</v>
       </c>
       <c r="W11" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
         <v>1</v>
@@ -1772,28 +1772,28 @@
         <v>1.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.26</v>
+        <v>1.55</v>
       </c>
       <c r="AH11" t="n">
         <v>1.3</v>
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="M12" t="n">
         <v>3.8</v>
       </c>
       <c r="N12" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="O12" t="n">
         <v>3.6</v>
@@ -1873,7 +1873,7 @@
         <v>3.58</v>
       </c>
       <c r="T12" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="U12" t="n">
         <v>1.63</v>
@@ -1894,10 +1894,10 @@
         <v>5.25</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="AC12" t="n">
         <v>2.12</v>
@@ -1909,7 +1909,7 @@
         <v>1.41</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AG12" t="n">
         <v>1.72</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.74</v>
+        <v>2.15</v>
       </c>
       <c r="M13" t="n">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="N13" t="n">
-        <v>5.1</v>
+        <v>2.9</v>
       </c>
       <c r="O13" t="n">
-        <v>2.55</v>
+        <v>2.64</v>
       </c>
       <c r="P13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V13" t="n">
+        <v>7</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB13" t="n">
         <v>1.85</v>
       </c>
-      <c r="Q13" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V13" t="n">
-        <v>13</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AC13" t="n">
-        <v>5.94</v>
+        <v>3</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.48</v>
+        <v>2.04</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.82</v>
+        <v>1.6</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46051.625</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="M14" t="n">
-        <v>3.2</v>
+        <v>2.45</v>
       </c>
       <c r="N14" t="n">
         <v>3.2</v>
       </c>
       <c r="O14" t="n">
-        <v>2.73</v>
+        <v>3.62</v>
       </c>
       <c r="P14" t="n">
-        <v>2.07</v>
+        <v>1.58</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.03</v>
+        <v>4</v>
       </c>
       <c r="R14" t="n">
-        <v>1.38</v>
+        <v>1.83</v>
       </c>
       <c r="S14" t="n">
-        <v>2.77</v>
+        <v>2.05</v>
       </c>
       <c r="T14" t="n">
-        <v>2.77</v>
+        <v>4.5</v>
       </c>
       <c r="U14" t="n">
-        <v>1.38</v>
+        <v>1.13</v>
       </c>
       <c r="V14" t="n">
-        <v>6.5</v>
+        <v>15</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.28</v>
+        <v>2</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.93</v>
+        <v>3.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.86</v>
+        <v>1.26</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.35</v>
+        <v>6.7</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.28</v>
+        <v>1.05</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.71</v>
+        <v>2.5</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.02</v>
+        <v>1.48</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.66</v>
+        <v>1.44</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46051.625</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,61 +2206,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.5</v>
+        <v>1.74</v>
       </c>
       <c r="M15" t="n">
-        <v>2.45</v>
+        <v>2.87</v>
       </c>
       <c r="N15" t="n">
-        <v>3.2</v>
+        <v>5.1</v>
       </c>
       <c r="O15" t="n">
-        <v>3.62</v>
+        <v>2.55</v>
       </c>
       <c r="P15" t="n">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="R15" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="S15" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="T15" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="U15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V15" t="n">
+        <v>13</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X15" t="n">
         <v>1.13</v>
       </c>
-      <c r="V15" t="n">
-        <v>15</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.18</v>
-      </c>
       <c r="Y15" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="Z15" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.1</v>
+        <v>2.74</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>6.7</v>
+        <v>5.94</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AE15" t="n">
         <v>2.5</v>
@@ -2269,10 +2269,10 @@
         <v>1.48</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.44</v>
+        <v>1.82</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46051.625</v>
@@ -2447,16 +2447,16 @@
         <v>1.8</v>
       </c>
       <c r="M17" t="n">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="N17" t="n">
-        <v>4.09</v>
+        <v>4.33</v>
       </c>
       <c r="O17" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="Q17" t="n">
         <v>4.5</v>
@@ -2471,7 +2471,7 @@
         <v>2.59</v>
       </c>
       <c r="U17" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="V17" t="n">
         <v>6.1</v>
@@ -2480,13 +2480,13 @@
         <v>1.07</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.1</v>
+        <v>3.54</v>
       </c>
       <c r="AA17" t="n">
         <v>1.83</v>
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="M18" t="n">
-        <v>3.16</v>
+        <v>3.3</v>
       </c>
       <c r="N18" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="O18" t="n">
         <v>3.05</v>
@@ -2584,13 +2584,13 @@
         <v>1.35</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>2.57</v>
       </c>
       <c r="T18" t="n">
         <v>2.93</v>
       </c>
       <c r="U18" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="V18" t="n">
         <v>7</v>
@@ -2602,7 +2602,7 @@
         <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z18" t="n">
         <v>3.18</v>
@@ -2623,7 +2623,7 @@
         <v>1.7</v>
       </c>
       <c r="AF18" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG18" t="n">
         <v>1.33</v>

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="V6" t="n">
+        <v>15</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC6" t="n">
         <v>7</v>
       </c>
-      <c r="M6" t="n">
-        <v>5</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="O6" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V6" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AD6" t="n">
-        <v>1.79</v>
+        <v>1.04</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.52</v>
+        <v>2.45</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.34</v>
+        <v>1.48</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.14</v>
+        <v>1.41</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.06</v>
+        <v>1.33</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46051.5</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.87</v>
+        <v>5.6</v>
       </c>
       <c r="M7" t="n">
-        <v>2.62</v>
+        <v>4.75</v>
       </c>
       <c r="N7" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="O7" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="P7" t="n">
-        <v>1.64</v>
+        <v>2.57</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.74</v>
+        <v>1.8</v>
       </c>
       <c r="R7" t="n">
-        <v>1.76</v>
+        <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.94</v>
+        <v>3.84</v>
       </c>
       <c r="T7" t="n">
-        <v>4.5</v>
+        <v>2.01</v>
       </c>
       <c r="U7" t="n">
-        <v>1.13</v>
+        <v>1.71</v>
       </c>
       <c r="V7" t="n">
-        <v>15</v>
+        <v>4.15</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>1.16</v>
       </c>
       <c r="X7" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.76</v>
+        <v>1.07</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.1</v>
+        <v>5.85</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.2</v>
+        <v>1.35</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.26</v>
+        <v>2.74</v>
       </c>
       <c r="AC7" t="n">
-        <v>7</v>
+        <v>1.95</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.04</v>
+        <v>1.79</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.45</v>
+        <v>1.52</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.48</v>
+        <v>2.34</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.41</v>
+        <v>2.66</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.33</v>
+        <v>1.06</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46051.5</v>
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.01</v>
+        <v>3.3</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N11" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="O11" t="n">
-        <v>3.65</v>
+        <v>4.05</v>
       </c>
       <c r="P11" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.83</v>
+        <v>2.74</v>
       </c>
       <c r="R11" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="S11" t="n">
-        <v>2.77</v>
+        <v>2.59</v>
       </c>
       <c r="T11" t="n">
-        <v>2.7</v>
+        <v>2.91</v>
       </c>
       <c r="U11" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="V11" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.34</v>
+        <v>3.05</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.86</v>
+        <v>2.03</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AC11" t="n">
         <v>3.15</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.66</v>
+        <v>1.77</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.07</v>
+        <v>1.92</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.55</v>
+        <v>1.27</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46051.60416666666</v>
@@ -1855,7 +1855,7 @@
         <v>3.8</v>
       </c>
       <c r="N12" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="O12" t="n">
         <v>3.6</v>
@@ -1882,7 +1882,7 @@
         <v>4.55</v>
       </c>
       <c r="W12" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
@@ -1897,7 +1897,7 @@
         <v>1.42</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.49</v>
+        <v>2.62</v>
       </c>
       <c r="AC12" t="n">
         <v>2.12</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="N13" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="O13" t="n">
-        <v>2.64</v>
+        <v>3.62</v>
       </c>
       <c r="P13" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="S13" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q13" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3</v>
-      </c>
       <c r="T13" t="n">
-        <v>2.77</v>
+        <v>4.5</v>
       </c>
       <c r="U13" t="n">
-        <v>1.38</v>
+        <v>1.13</v>
       </c>
       <c r="V13" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.28</v>
+        <v>2</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.93</v>
+        <v>3.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.85</v>
+        <v>1.26</v>
       </c>
       <c r="AC13" t="n">
-        <v>3</v>
+        <v>6.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.28</v>
+        <v>1.05</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.04</v>
+        <v>1.48</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46051.625</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,61 +2087,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.5</v>
+        <v>1.74</v>
       </c>
       <c r="M14" t="n">
-        <v>2.45</v>
+        <v>2.87</v>
       </c>
       <c r="N14" t="n">
-        <v>3.2</v>
+        <v>5.1</v>
       </c>
       <c r="O14" t="n">
-        <v>3.62</v>
+        <v>2.55</v>
       </c>
       <c r="P14" t="n">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="Q14" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="R14" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="S14" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="T14" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="U14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V14" t="n">
+        <v>13</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X14" t="n">
         <v>1.13</v>
       </c>
-      <c r="V14" t="n">
-        <v>15</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.18</v>
-      </c>
       <c r="Y14" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="Z14" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.1</v>
+        <v>2.74</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.7</v>
+        <v>5.94</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AE14" t="n">
         <v>2.5</v>
@@ -2150,10 +2150,10 @@
         <v>1.48</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.44</v>
+        <v>1.82</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46051.625</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.74</v>
+        <v>2.15</v>
       </c>
       <c r="M15" t="n">
-        <v>2.87</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>5.1</v>
+        <v>2.9</v>
       </c>
       <c r="O15" t="n">
-        <v>2.55</v>
+        <v>2.84</v>
       </c>
       <c r="P15" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V15" t="n">
+        <v>7</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB15" t="n">
         <v>1.85</v>
       </c>
-      <c r="Q15" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V15" t="n">
-        <v>13</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AC15" t="n">
-        <v>5.94</v>
+        <v>3</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.48</v>
+        <v>2.04</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.82</v>
+        <v>1.61</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46051.625</v>

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="M2" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="N2" t="n">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -1022,7 +1022,7 @@
         <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="O5" t="n">
         <v>4.5</v>
@@ -1061,10 +1061,10 @@
         <v>5.97</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="AC5" t="n">
         <v>1.94</v>
@@ -1073,10 +1073,10 @@
         <v>1.77</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="AG5" t="n">
         <v>1.14</v>
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="M6" t="n">
         <v>2.62</v>
       </c>
       <c r="N6" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="O6" t="n">
         <v>4.2</v>
@@ -1153,13 +1153,13 @@
         <v>3.74</v>
       </c>
       <c r="R6" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="S6" t="n">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="T6" t="n">
-        <v>4.5</v>
+        <v>4.35</v>
       </c>
       <c r="U6" t="n">
         <v>1.13</v>
@@ -1174,16 +1174,16 @@
         <v>1.12</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AC6" t="n">
         <v>7</v>
@@ -1198,7 +1198,7 @@
         <v>1.48</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AH6" t="n">
         <v>1.33</v>
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="M10" t="n">
         <v>3.5</v>
       </c>
       <c r="N10" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="O10" t="n">
         <v>2.22</v>
@@ -1626,7 +1626,7 @@
         <v>2.23</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.84</v>
+        <v>4.81</v>
       </c>
       <c r="R10" t="n">
         <v>1.28</v>
@@ -1647,13 +1647,13 @@
         <v>1.07</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
         <v>1.16</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.15</v>
+        <v>4.27</v>
       </c>
       <c r="AA10" t="n">
         <v>1.64</v>
@@ -1662,19 +1662,19 @@
         <v>2.12</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="AD10" t="n">
         <v>1.4</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AF10" t="n">
         <v>2.12</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AH10" t="n">
         <v>2.05</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1733,70 +1733,70 @@
         <v>3.3</v>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="N11" t="n">
         <v>2</v>
       </c>
       <c r="O11" t="n">
-        <v>4.05</v>
+        <v>3.6</v>
       </c>
       <c r="P11" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.74</v>
+        <v>2.42</v>
       </c>
       <c r="R11" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V11" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AE11" t="n">
         <v>1.41</v>
       </c>
-      <c r="S11" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AF11" t="n">
-        <v>1.92</v>
+        <v>2.6</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.27</v>
+        <v>1.72</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46051.60416666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1852,70 +1852,70 @@
         <v>3.3</v>
       </c>
       <c r="M12" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="N12" t="n">
         <v>2</v>
       </c>
       <c r="O12" t="n">
-        <v>3.6</v>
+        <v>4.05</v>
       </c>
       <c r="P12" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.42</v>
+        <v>2.74</v>
       </c>
       <c r="R12" t="n">
-        <v>1.21</v>
+        <v>1.41</v>
       </c>
       <c r="S12" t="n">
-        <v>3.58</v>
+        <v>2.59</v>
       </c>
       <c r="T12" t="n">
-        <v>2.13</v>
+        <v>2.91</v>
       </c>
       <c r="U12" t="n">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="V12" t="n">
-        <v>4.55</v>
+        <v>7.4</v>
       </c>
       <c r="W12" t="n">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.25</v>
+        <v>3.05</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.42</v>
+        <v>2.03</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.62</v>
+        <v>1.73</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.12</v>
+        <v>3.15</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.64</v>
+        <v>1.24</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.41</v>
+        <v>1.77</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.6</v>
+        <v>1.92</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.72</v>
+        <v>1.27</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46051.60416666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,61 +1968,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.5</v>
+        <v>1.74</v>
       </c>
       <c r="M13" t="n">
-        <v>2.45</v>
+        <v>2.87</v>
       </c>
       <c r="N13" t="n">
-        <v>3.2</v>
+        <v>5.1</v>
       </c>
       <c r="O13" t="n">
-        <v>3.62</v>
+        <v>2.55</v>
       </c>
       <c r="P13" t="n">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="Q13" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="R13" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="S13" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="T13" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="U13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V13" t="n">
+        <v>13</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X13" t="n">
         <v>1.13</v>
       </c>
-      <c r="V13" t="n">
-        <v>15</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.18</v>
-      </c>
       <c r="Y13" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="Z13" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.1</v>
+        <v>2.74</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="AC13" t="n">
-        <v>6.7</v>
+        <v>5.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AE13" t="n">
         <v>2.5</v>
@@ -2031,10 +2031,10 @@
         <v>1.48</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.33</v>
+        <v>1.1</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.44</v>
+        <v>1.84</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46051.625</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.74</v>
+        <v>2.15</v>
       </c>
       <c r="M14" t="n">
-        <v>2.87</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>5.1</v>
+        <v>2.9</v>
       </c>
       <c r="O14" t="n">
-        <v>2.55</v>
+        <v>2.84</v>
       </c>
       <c r="P14" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V14" t="n">
+        <v>7</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB14" t="n">
         <v>1.85</v>
       </c>
-      <c r="Q14" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V14" t="n">
-        <v>13</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AC14" t="n">
-        <v>5.94</v>
+        <v>3</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.48</v>
+        <v>2.04</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.82</v>
+        <v>1.61</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46051.625</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.15</v>
+        <v>2.49</v>
       </c>
       <c r="M15" t="n">
-        <v>3.2</v>
+        <v>2.45</v>
       </c>
       <c r="N15" t="n">
-        <v>2.9</v>
+        <v>3.61</v>
       </c>
       <c r="O15" t="n">
-        <v>2.84</v>
+        <v>3.6</v>
       </c>
       <c r="P15" t="n">
-        <v>2.11</v>
+        <v>1.59</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.4</v>
+        <v>5.05</v>
       </c>
       <c r="R15" t="n">
-        <v>1.36</v>
+        <v>1.83</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="T15" t="n">
-        <v>2.84</v>
+        <v>4.5</v>
       </c>
       <c r="U15" t="n">
-        <v>1.38</v>
+        <v>1.13</v>
       </c>
       <c r="V15" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="W15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AD15" t="n">
         <v>1.04</v>
       </c>
-      <c r="X15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AE15" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.04</v>
+        <v>1.48</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.32</v>
+        <v>1.46</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.61</v>
+        <v>1.42</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46051.625</v>

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1733,70 +1733,70 @@
         <v>3.3</v>
       </c>
       <c r="M11" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="N11" t="n">
         <v>2</v>
       </c>
       <c r="O11" t="n">
-        <v>3.6</v>
+        <v>4.05</v>
       </c>
       <c r="P11" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.42</v>
+        <v>2.74</v>
       </c>
       <c r="R11" t="n">
-        <v>1.21</v>
+        <v>1.41</v>
       </c>
       <c r="S11" t="n">
-        <v>3.58</v>
+        <v>2.59</v>
       </c>
       <c r="T11" t="n">
-        <v>2.13</v>
+        <v>2.91</v>
       </c>
       <c r="U11" t="n">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="V11" t="n">
-        <v>4.55</v>
+        <v>7.4</v>
       </c>
       <c r="W11" t="n">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.25</v>
+        <v>3.05</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.42</v>
+        <v>2.03</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.62</v>
+        <v>1.73</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.12</v>
+        <v>3.15</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.64</v>
+        <v>1.24</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.41</v>
+        <v>1.77</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.6</v>
+        <v>1.92</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.72</v>
+        <v>1.27</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46051.60416666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1852,70 +1852,70 @@
         <v>3.3</v>
       </c>
       <c r="M12" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="N12" t="n">
         <v>2</v>
       </c>
       <c r="O12" t="n">
-        <v>4.05</v>
+        <v>3.6</v>
       </c>
       <c r="P12" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.74</v>
+        <v>2.42</v>
       </c>
       <c r="R12" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V12" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AE12" t="n">
         <v>1.41</v>
       </c>
-      <c r="S12" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AF12" t="n">
-        <v>1.92</v>
+        <v>2.6</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.27</v>
+        <v>1.72</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46051.60416666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.15</v>
+        <v>2.49</v>
       </c>
       <c r="M14" t="n">
-        <v>3.2</v>
+        <v>2.45</v>
       </c>
       <c r="N14" t="n">
-        <v>2.9</v>
+        <v>3.61</v>
       </c>
       <c r="O14" t="n">
-        <v>2.84</v>
+        <v>3.6</v>
       </c>
       <c r="P14" t="n">
-        <v>2.11</v>
+        <v>1.59</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.4</v>
+        <v>5.05</v>
       </c>
       <c r="R14" t="n">
-        <v>1.36</v>
+        <v>1.83</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="T14" t="n">
-        <v>2.84</v>
+        <v>4.5</v>
       </c>
       <c r="U14" t="n">
-        <v>1.38</v>
+        <v>1.13</v>
       </c>
       <c r="V14" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="W14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AD14" t="n">
         <v>1.04</v>
       </c>
-      <c r="X14" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AE14" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.04</v>
+        <v>1.48</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.32</v>
+        <v>1.46</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.61</v>
+        <v>1.42</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46051.625</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.49</v>
+        <v>2.15</v>
       </c>
       <c r="M15" t="n">
-        <v>2.45</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>3.61</v>
+        <v>2.9</v>
       </c>
       <c r="O15" t="n">
-        <v>3.6</v>
+        <v>2.64</v>
       </c>
       <c r="P15" t="n">
-        <v>1.59</v>
+        <v>2.04</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.05</v>
+        <v>3.88</v>
       </c>
       <c r="R15" t="n">
-        <v>1.83</v>
+        <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="T15" t="n">
-        <v>4.5</v>
+        <v>2.84</v>
       </c>
       <c r="U15" t="n">
-        <v>1.13</v>
+        <v>1.38</v>
       </c>
       <c r="V15" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE15" t="n">
         <v>1.7</v>
       </c>
-      <c r="Z15" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AF15" t="n">
-        <v>1.48</v>
+        <v>2.04</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46051.625</v>

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="M6" t="n">
         <v>2.62</v>
       </c>
       <c r="N6" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="O6" t="n">
         <v>4.2</v>
@@ -1153,10 +1153,10 @@
         <v>3.74</v>
       </c>
       <c r="R6" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="S6" t="n">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="T6" t="n">
         <v>4.35</v>
@@ -1174,7 +1174,7 @@
         <v>1.12</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="Z6" t="n">
         <v>2</v>
@@ -1183,7 +1183,7 @@
         <v>3.42</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AC6" t="n">
         <v>7</v>
@@ -1198,10 +1198,10 @@
         <v>1.48</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46051.5</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1733,70 +1733,70 @@
         <v>3.3</v>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="N11" t="n">
         <v>2</v>
       </c>
       <c r="O11" t="n">
-        <v>4.05</v>
+        <v>3.6</v>
       </c>
       <c r="P11" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.74</v>
+        <v>2.42</v>
       </c>
       <c r="R11" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V11" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AE11" t="n">
         <v>1.41</v>
       </c>
-      <c r="S11" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AF11" t="n">
-        <v>1.92</v>
+        <v>2.6</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.27</v>
+        <v>1.72</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46051.60416666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1852,70 +1852,70 @@
         <v>3.3</v>
       </c>
       <c r="M12" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="N12" t="n">
         <v>2</v>
       </c>
       <c r="O12" t="n">
-        <v>3.6</v>
+        <v>4.05</v>
       </c>
       <c r="P12" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.42</v>
+        <v>2.74</v>
       </c>
       <c r="R12" t="n">
-        <v>1.21</v>
+        <v>1.41</v>
       </c>
       <c r="S12" t="n">
-        <v>3.58</v>
+        <v>2.59</v>
       </c>
       <c r="T12" t="n">
-        <v>2.13</v>
+        <v>2.91</v>
       </c>
       <c r="U12" t="n">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="V12" t="n">
-        <v>4.55</v>
+        <v>7.4</v>
       </c>
       <c r="W12" t="n">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.25</v>
+        <v>3.05</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.42</v>
+        <v>2.03</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.62</v>
+        <v>1.73</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.12</v>
+        <v>3.15</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.64</v>
+        <v>1.24</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.41</v>
+        <v>1.77</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.6</v>
+        <v>1.92</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.72</v>
+        <v>1.27</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46051.60416666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.74</v>
+        <v>2.15</v>
       </c>
       <c r="M13" t="n">
-        <v>2.87</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>5.1</v>
+        <v>2.9</v>
       </c>
       <c r="O13" t="n">
-        <v>2.55</v>
+        <v>2.64</v>
       </c>
       <c r="P13" t="n">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.25</v>
+        <v>3.88</v>
       </c>
       <c r="R13" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="S13" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="T13" t="n">
-        <v>3.8</v>
+        <v>2.84</v>
       </c>
       <c r="U13" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="V13" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.25</v>
+        <v>3.51</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.74</v>
+        <v>1.96</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.35</v>
+        <v>1.86</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.4</v>
+        <v>3</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.48</v>
+        <v>2.04</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.1</v>
+        <v>1.33</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.84</v>
+        <v>1.51</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46051.625</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,61 +2087,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.49</v>
+        <v>1.74</v>
       </c>
       <c r="M14" t="n">
-        <v>2.45</v>
+        <v>2.87</v>
       </c>
       <c r="N14" t="n">
-        <v>3.61</v>
+        <v>5.1</v>
       </c>
       <c r="O14" t="n">
-        <v>3.6</v>
+        <v>2.55</v>
       </c>
       <c r="P14" t="n">
-        <v>1.59</v>
+        <v>1.85</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.05</v>
+        <v>5.25</v>
       </c>
       <c r="R14" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="S14" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="T14" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="U14" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="V14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.1</v>
+        <v>2.74</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.75</v>
+        <v>5.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AE14" t="n">
         <v>2.5</v>
@@ -2150,10 +2150,10 @@
         <v>1.48</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.42</v>
+        <v>1.84</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46051.625</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="M15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N15" t="n">
         <v>3.2</v>
       </c>
-      <c r="N15" t="n">
-        <v>2.9</v>
-      </c>
       <c r="O15" t="n">
-        <v>2.64</v>
+        <v>3.6</v>
       </c>
       <c r="P15" t="n">
-        <v>2.04</v>
+        <v>1.59</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.88</v>
+        <v>5.05</v>
       </c>
       <c r="R15" t="n">
-        <v>1.36</v>
+        <v>1.83</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>1.87</v>
       </c>
       <c r="T15" t="n">
-        <v>2.84</v>
+        <v>4.5</v>
       </c>
       <c r="U15" t="n">
-        <v>1.38</v>
+        <v>1.13</v>
       </c>
       <c r="V15" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="W15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AD15" t="n">
         <v>1.04</v>
       </c>
-      <c r="X15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AE15" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.04</v>
+        <v>1.48</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46051.625</v>

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.15</v>
+        <v>1.74</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2</v>
+        <v>2.87</v>
       </c>
       <c r="N13" t="n">
-        <v>2.9</v>
+        <v>5.1</v>
       </c>
       <c r="O13" t="n">
-        <v>2.64</v>
+        <v>2.55</v>
       </c>
       <c r="P13" t="n">
-        <v>2.04</v>
+        <v>1.85</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.88</v>
+        <v>5.25</v>
       </c>
       <c r="R13" t="n">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="T13" t="n">
-        <v>2.84</v>
+        <v>3.8</v>
       </c>
       <c r="U13" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="V13" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.51</v>
+        <v>2.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.96</v>
+        <v>2.74</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.86</v>
+        <v>1.35</v>
       </c>
       <c r="AC13" t="n">
-        <v>3</v>
+        <v>5.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.33</v>
+        <v>1.09</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.04</v>
+        <v>1.48</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.51</v>
+        <v>1.84</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46051.625</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,61 +2087,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.74</v>
+        <v>2.5</v>
       </c>
       <c r="M14" t="n">
-        <v>2.87</v>
+        <v>2.5</v>
       </c>
       <c r="N14" t="n">
-        <v>5.1</v>
+        <v>3.2</v>
       </c>
       <c r="O14" t="n">
-        <v>2.55</v>
+        <v>3.6</v>
       </c>
       <c r="P14" t="n">
-        <v>1.85</v>
+        <v>1.59</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.25</v>
+        <v>5.05</v>
       </c>
       <c r="R14" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="T14" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="U14" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="V14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.55</v>
+        <v>1.81</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.4</v>
+        <v>6.75</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AE14" t="n">
         <v>2.5</v>
@@ -2150,10 +2150,10 @@
         <v>1.48</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.31</v>
+        <v>1.46</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.84</v>
+        <v>1.42</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46051.625</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="M15" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="O15" t="n">
-        <v>3.6</v>
+        <v>2.64</v>
       </c>
       <c r="P15" t="n">
-        <v>1.59</v>
+        <v>2.04</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.05</v>
+        <v>3.88</v>
       </c>
       <c r="R15" t="n">
-        <v>1.83</v>
+        <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>1.87</v>
+        <v>3</v>
       </c>
       <c r="T15" t="n">
-        <v>4.5</v>
+        <v>2.84</v>
       </c>
       <c r="U15" t="n">
-        <v>1.13</v>
+        <v>1.38</v>
       </c>
       <c r="V15" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.81</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>2</v>
+        <v>3.51</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.1</v>
+        <v>1.96</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.26</v>
+        <v>1.86</v>
       </c>
       <c r="AC15" t="n">
-        <v>6.75</v>
+        <v>3</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.04</v>
+        <v>1.33</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.48</v>
+        <v>2.04</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46051.625</v>
@@ -2444,70 +2444,70 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="M17" t="n">
-        <v>3.6</v>
+        <v>3.51</v>
       </c>
       <c r="N17" t="n">
-        <v>4.33</v>
+        <v>4.15</v>
       </c>
       <c r="O17" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="P17" t="n">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
         <v>4.5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S17" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="T17" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="U17" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="V17" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="W17" t="n">
         <v>1.07</v>
       </c>
       <c r="X17" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AH17" t="n">
         <v>1.95</v>
@@ -2566,31 +2566,31 @@
         <v>2.45</v>
       </c>
       <c r="M18" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="O18" t="n">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="P18" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="Q18" t="n">
         <v>3.4</v>
       </c>
       <c r="R18" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="S18" t="n">
-        <v>2.57</v>
+        <v>2.53</v>
       </c>
       <c r="T18" t="n">
-        <v>2.93</v>
+        <v>2.65</v>
       </c>
       <c r="U18" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="V18" t="n">
         <v>7</v>
@@ -2599,28 +2599,28 @@
         <v>1.04</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB18" t="n">
         <v>1.84</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AF18" t="n">
         <v>2.05</v>

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="M2" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="N2" t="n">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -975,7 +975,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1016,19 +1016,19 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.41</v>
+        <v>4.33</v>
       </c>
       <c r="M5" t="n">
         <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="O5" t="n">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="P5" t="n">
-        <v>2.73</v>
+        <v>2.51</v>
       </c>
       <c r="Q5" t="n">
         <v>2</v>
@@ -1046,7 +1046,7 @@
         <v>1.72</v>
       </c>
       <c r="V5" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="W5" t="n">
         <v>1.15</v>
@@ -1058,19 +1058,19 @@
         <v>1.06</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.97</v>
+        <v>6.15</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="AC5" t="n">
         <v>1.94</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AE5" t="n">
         <v>1.41</v>
@@ -1079,13 +1079,13 @@
         <v>2.66</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.14</v>
+        <v>2.16</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AI5" s="3" t="n">
-        <v>46051.47916666666</v>
+        <v>46051.48958333334</v>
       </c>
     </row>
     <row r="6">
@@ -1150,7 +1150,7 @@
         <v>1.64</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="R6" t="n">
         <v>1.76</v>
@@ -1171,7 +1171,7 @@
         <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="Y6" t="n">
         <v>1.76</v>
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>5.6</v>
+        <v>4.59</v>
       </c>
       <c r="M7" t="n">
-        <v>4.75</v>
+        <v>4.65</v>
       </c>
       <c r="N7" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="O7" t="n">
-        <v>5.8</v>
+        <v>4.7</v>
       </c>
       <c r="P7" t="n">
-        <v>2.57</v>
+        <v>2.77</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="R7" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="S7" t="n">
-        <v>3.84</v>
+        <v>4.15</v>
       </c>
       <c r="T7" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="U7" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="V7" t="n">
-        <v>4.15</v>
+        <v>3.95</v>
       </c>
       <c r="W7" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.85</v>
+        <v>6.25</v>
       </c>
       <c r="AA7" t="n">
         <v>1.35</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.74</v>
+        <v>3.07</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.34</v>
+        <v>2.62</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.66</v>
+        <v>1.18</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46051.5</v>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1614,7 +1614,7 @@
         <v>1.66</v>
       </c>
       <c r="M10" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="N10" t="n">
         <v>4.33</v>
@@ -1659,7 +1659,7 @@
         <v>1.64</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="AC10" t="n">
         <v>2.56</v>
@@ -1668,7 +1668,7 @@
         <v>1.4</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AF10" t="n">
         <v>2.12</v>
@@ -1677,10 +1677,10 @@
         <v>1.19</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>46051.5625</v>
+        <v>46051.57291666666</v>
       </c>
     </row>
     <row r="11">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="M11" t="n">
-        <v>3.8</v>
+        <v>3.49</v>
       </c>
       <c r="N11" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="O11" t="n">
-        <v>3.6</v>
+        <v>4.18</v>
       </c>
       <c r="P11" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.42</v>
+        <v>2.59</v>
       </c>
       <c r="R11" t="n">
-        <v>1.21</v>
+        <v>1.37</v>
       </c>
       <c r="S11" t="n">
-        <v>3.58</v>
+        <v>2.74</v>
       </c>
       <c r="T11" t="n">
-        <v>2.13</v>
+        <v>2.63</v>
       </c>
       <c r="U11" t="n">
-        <v>1.63</v>
+        <v>1.34</v>
       </c>
       <c r="V11" t="n">
-        <v>4.55</v>
+        <v>7.2</v>
       </c>
       <c r="W11" t="n">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.09</v>
+        <v>1.27</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.25</v>
+        <v>3.14</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.42</v>
+        <v>1.95</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.62</v>
+        <v>1.76</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.12</v>
+        <v>3.15</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.64</v>
+        <v>1.28</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.41</v>
+        <v>1.78</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.72</v>
+        <v>1.24</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46051.60416666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.3</v>
+        <v>3.23</v>
       </c>
       <c r="M12" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="N12" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="O12" t="n">
-        <v>4.05</v>
+        <v>3.72</v>
       </c>
       <c r="P12" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.74</v>
+        <v>2.42</v>
       </c>
       <c r="R12" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V12" t="n">
+        <v>5</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AE12" t="n">
         <v>1.41</v>
       </c>
-      <c r="S12" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AF12" t="n">
-        <v>1.92</v>
+        <v>2.6</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46051.60416666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.74</v>
+        <v>2.15</v>
       </c>
       <c r="M13" t="n">
-        <v>2.87</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>5.1</v>
+        <v>2.9</v>
       </c>
       <c r="O13" t="n">
-        <v>2.55</v>
+        <v>2.64</v>
       </c>
       <c r="P13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V13" t="n">
+        <v>7</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB13" t="n">
         <v>1.85</v>
       </c>
-      <c r="Q13" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V13" t="n">
-        <v>13</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AC13" t="n">
-        <v>5.4</v>
+        <v>3</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.09</v>
+        <v>1.28</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.48</v>
+        <v>2.04</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.84</v>
+        <v>1.51</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46051.625</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.5</v>
+        <v>1.74</v>
       </c>
       <c r="M14" t="n">
-        <v>2.5</v>
+        <v>2.87</v>
       </c>
       <c r="N14" t="n">
-        <v>3.2</v>
+        <v>5.1</v>
       </c>
       <c r="O14" t="n">
-        <v>3.6</v>
+        <v>2.56</v>
       </c>
       <c r="P14" t="n">
-        <v>1.59</v>
+        <v>1.91</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.05</v>
+        <v>6.41</v>
       </c>
       <c r="R14" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="S14" t="n">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="T14" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="U14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V14" t="n">
+        <v>13</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X14" t="n">
         <v>1.13</v>
       </c>
-      <c r="V14" t="n">
-        <v>15</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.14</v>
-      </c>
       <c r="Y14" t="n">
-        <v>1.81</v>
+        <v>1.55</v>
       </c>
       <c r="Z14" t="n">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.1</v>
+        <v>2.74</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.75</v>
+        <v>5.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AE14" t="n">
         <v>2.5</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.42</v>
+        <v>1.83</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46051.625</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="M15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N15" t="n">
         <v>3.2</v>
       </c>
-      <c r="N15" t="n">
-        <v>2.9</v>
-      </c>
       <c r="O15" t="n">
-        <v>2.64</v>
+        <v>3.46</v>
       </c>
       <c r="P15" t="n">
-        <v>2.04</v>
+        <v>1.72</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.88</v>
+        <v>4.35</v>
       </c>
       <c r="R15" t="n">
-        <v>1.36</v>
+        <v>1.75</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>1.87</v>
       </c>
       <c r="T15" t="n">
-        <v>2.84</v>
+        <v>4.5</v>
       </c>
       <c r="U15" t="n">
-        <v>1.38</v>
+        <v>1.13</v>
       </c>
       <c r="V15" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>1.81</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.51</v>
+        <v>2.05</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.96</v>
+        <v>3.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.86</v>
+        <v>1.25</v>
       </c>
       <c r="AC15" t="n">
-        <v>3</v>
+        <v>6.75</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.33</v>
+        <v>1.09</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.04</v>
+        <v>1.48</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46051.625</v>

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.87</v>
+        <v>4.84</v>
       </c>
       <c r="M6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="O6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P6" t="n">
         <v>2.62</v>
       </c>
-      <c r="N6" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.64</v>
-      </c>
       <c r="Q6" t="n">
-        <v>3.72</v>
+        <v>1.95</v>
       </c>
       <c r="R6" t="n">
-        <v>1.76</v>
+        <v>1.2</v>
       </c>
       <c r="S6" t="n">
-        <v>1.94</v>
+        <v>4</v>
       </c>
       <c r="T6" t="n">
-        <v>4.35</v>
+        <v>1.91</v>
       </c>
       <c r="U6" t="n">
-        <v>1.13</v>
+        <v>1.77</v>
       </c>
       <c r="V6" t="n">
-        <v>15</v>
+        <v>4.1</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="X6" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.76</v>
+        <v>1.06</v>
       </c>
       <c r="Z6" t="n">
-        <v>2</v>
+        <v>6.25</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.42</v>
+        <v>1.32</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.26</v>
+        <v>2.88</v>
       </c>
       <c r="AC6" t="n">
-        <v>7</v>
+        <v>1.89</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.04</v>
+        <v>1.81</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.45</v>
+        <v>1.42</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.48</v>
+        <v>2.62</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.41</v>
+        <v>2.31</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46051.5</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.59</v>
+        <v>2.87</v>
       </c>
       <c r="M7" t="n">
-        <v>4.65</v>
+        <v>2.62</v>
       </c>
       <c r="N7" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="O7" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="P7" t="n">
-        <v>2.77</v>
+        <v>1.64</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.96</v>
+        <v>3.72</v>
       </c>
       <c r="R7" t="n">
-        <v>1.16</v>
+        <v>1.76</v>
       </c>
       <c r="S7" t="n">
-        <v>4.15</v>
+        <v>1.94</v>
       </c>
       <c r="T7" t="n">
-        <v>1.95</v>
+        <v>4.35</v>
       </c>
       <c r="U7" t="n">
-        <v>1.75</v>
+        <v>1.13</v>
       </c>
       <c r="V7" t="n">
-        <v>3.95</v>
+        <v>15</v>
       </c>
       <c r="W7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X7" t="n">
         <v>1.17</v>
       </c>
-      <c r="X7" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y7" t="n">
-        <v>1.06</v>
+        <v>1.76</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.25</v>
+        <v>2</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.35</v>
+        <v>3.42</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.07</v>
+        <v>1.26</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.89</v>
+        <v>7</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.81</v>
+        <v>1.04</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.42</v>
+        <v>2.45</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.62</v>
+        <v>1.48</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46051.5</v>
@@ -1730,55 +1730,55 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.25</v>
+        <v>3.36</v>
       </c>
       <c r="M11" t="n">
-        <v>3.49</v>
+        <v>3.51</v>
       </c>
       <c r="N11" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="O11" t="n">
-        <v>4.18</v>
+        <v>3.6</v>
       </c>
       <c r="P11" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="R11" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="S11" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="T11" t="n">
-        <v>2.63</v>
+        <v>2.73</v>
       </c>
       <c r="U11" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="V11" t="n">
-        <v>7.2</v>
+        <v>6.55</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.14</v>
+        <v>3.42</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="AC11" t="n">
         <v>3.15</v>
@@ -1787,16 +1787,16 @@
         <v>1.28</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.9</v>
+        <v>2.03</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.24</v>
+        <v>1.69</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46051.60416666666</v>
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.23</v>
+        <v>3.2</v>
       </c>
       <c r="M12" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="N12" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="O12" t="n">
         <v>3.72</v>
@@ -1864,13 +1864,13 @@
         <v>2.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="R12" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S12" t="n">
-        <v>3.58</v>
+        <v>3.9</v>
       </c>
       <c r="T12" t="n">
         <v>2.13</v>
@@ -1879,7 +1879,7 @@
         <v>1.63</v>
       </c>
       <c r="V12" t="n">
-        <v>5</v>
+        <v>4.55</v>
       </c>
       <c r="W12" t="n">
         <v>1.13</v>
@@ -1897,7 +1897,7 @@
         <v>1.46</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.49</v>
+        <v>2.62</v>
       </c>
       <c r="AC12" t="n">
         <v>2.12</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="M13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N13" t="n">
         <v>3.2</v>
       </c>
-      <c r="N13" t="n">
-        <v>2.9</v>
-      </c>
       <c r="O13" t="n">
-        <v>2.64</v>
+        <v>3.46</v>
       </c>
       <c r="P13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="T13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="V13" t="n">
+        <v>15</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Z13" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q13" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V13" t="n">
-        <v>7</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3.25</v>
-      </c>
       <c r="AA13" t="n">
-        <v>1.93</v>
+        <v>3.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.85</v>
+        <v>1.25</v>
       </c>
       <c r="AC13" t="n">
-        <v>3</v>
+        <v>6.75</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.28</v>
+        <v>1.09</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.04</v>
+        <v>1.48</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.32</v>
+        <v>1.46</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46051.625</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="M15" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="O15" t="n">
-        <v>3.46</v>
+        <v>2.64</v>
       </c>
       <c r="P15" t="n">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.35</v>
+        <v>3.88</v>
       </c>
       <c r="R15" t="n">
-        <v>1.75</v>
+        <v>1.39</v>
       </c>
       <c r="S15" t="n">
-        <v>1.87</v>
+        <v>2.73</v>
       </c>
       <c r="T15" t="n">
-        <v>4.5</v>
+        <v>2.84</v>
       </c>
       <c r="U15" t="n">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="V15" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.81</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.05</v>
+        <v>3.25</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.1</v>
+        <v>1.93</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.25</v>
+        <v>1.85</v>
       </c>
       <c r="AC15" t="n">
-        <v>6.75</v>
+        <v>3</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.09</v>
+        <v>1.28</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.48</v>
+        <v>2.04</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46051.625</v>

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -662,10 +662,10 @@
         <v>2.5</v>
       </c>
       <c r="M2" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="N2" t="n">
-        <v>3</v>
+        <v>3.03</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.74</v>
+        <v>2.15</v>
       </c>
       <c r="M14" t="n">
-        <v>2.87</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>5.1</v>
+        <v>2.9</v>
       </c>
       <c r="O14" t="n">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="P14" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.41</v>
+        <v>3.88</v>
       </c>
       <c r="R14" t="n">
-        <v>1.65</v>
+        <v>1.39</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1</v>
+        <v>2.73</v>
       </c>
       <c r="T14" t="n">
-        <v>3.8</v>
+        <v>2.84</v>
       </c>
       <c r="U14" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="V14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.19</v>
+        <v>3.25</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.74</v>
+        <v>1.93</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.35</v>
+        <v>1.85</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.4</v>
+        <v>3</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.09</v>
+        <v>1.28</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.44</v>
+        <v>2.04</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.83</v>
+        <v>1.51</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46051.625</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.15</v>
+        <v>1.74</v>
       </c>
       <c r="M15" t="n">
-        <v>3.2</v>
+        <v>2.87</v>
       </c>
       <c r="N15" t="n">
-        <v>2.9</v>
+        <v>5.1</v>
       </c>
       <c r="O15" t="n">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="P15" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.88</v>
+        <v>6.41</v>
       </c>
       <c r="R15" t="n">
-        <v>1.39</v>
+        <v>1.65</v>
       </c>
       <c r="S15" t="n">
-        <v>2.73</v>
+        <v>2.1</v>
       </c>
       <c r="T15" t="n">
-        <v>2.84</v>
+        <v>3.8</v>
       </c>
       <c r="U15" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="V15" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.25</v>
+        <v>2.19</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.93</v>
+        <v>2.74</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.85</v>
+        <v>1.35</v>
       </c>
       <c r="AC15" t="n">
-        <v>3</v>
+        <v>5.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.28</v>
+        <v>1.09</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.04</v>
+        <v>1.44</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.51</v>
+        <v>1.83</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46051.625</v>

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4.84</v>
+        <v>2.91</v>
       </c>
       <c r="M6" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="N6" t="n">
-        <v>1.49</v>
+        <v>2.64</v>
       </c>
       <c r="O6" t="n">
-        <v>4.6</v>
+        <v>4.15</v>
       </c>
       <c r="P6" t="n">
-        <v>2.62</v>
+        <v>1.64</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.95</v>
+        <v>3.4</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2</v>
+        <v>1.78</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>2.11</v>
       </c>
       <c r="T6" t="n">
-        <v>1.91</v>
+        <v>4.55</v>
       </c>
       <c r="U6" t="n">
-        <v>1.77</v>
+        <v>1.18</v>
       </c>
       <c r="V6" t="n">
-        <v>4.1</v>
+        <v>11.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.17</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.06</v>
+        <v>1.73</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.25</v>
+        <v>1.99</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.32</v>
+        <v>3.35</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.88</v>
+        <v>1.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.89</v>
+        <v>7.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.81</v>
+        <v>1.04</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.42</v>
+        <v>2.3</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.62</v>
+        <v>1.53</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.31</v>
+        <v>1.38</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46051.5</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.87</v>
+        <v>5</v>
       </c>
       <c r="M7" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="O7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P7" t="n">
         <v>2.62</v>
       </c>
-      <c r="N7" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.64</v>
-      </c>
       <c r="Q7" t="n">
-        <v>3.72</v>
+        <v>1.84</v>
       </c>
       <c r="R7" t="n">
-        <v>1.76</v>
+        <v>1.16</v>
       </c>
       <c r="S7" t="n">
-        <v>1.94</v>
+        <v>4</v>
       </c>
       <c r="T7" t="n">
-        <v>4.35</v>
+        <v>1.95</v>
       </c>
       <c r="U7" t="n">
-        <v>1.13</v>
+        <v>1.75</v>
       </c>
       <c r="V7" t="n">
-        <v>15</v>
+        <v>4.1</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="X7" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.76</v>
+        <v>1.1</v>
       </c>
       <c r="Z7" t="n">
-        <v>2</v>
+        <v>6.25</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.42</v>
+        <v>1.32</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.26</v>
+        <v>2.88</v>
       </c>
       <c r="AC7" t="n">
-        <v>7</v>
+        <v>1.89</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.04</v>
+        <v>1.81</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.45</v>
+        <v>1.42</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.48</v>
+        <v>2.62</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.41</v>
+        <v>2.31</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46051.5</v>
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.36</v>
+        <v>3.4</v>
       </c>
       <c r="M11" t="n">
-        <v>3.51</v>
+        <v>3.2</v>
       </c>
       <c r="N11" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="O11" t="n">
         <v>3.6</v>
@@ -1745,25 +1745,25 @@
         <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="R11" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="T11" t="n">
         <v>2.73</v>
       </c>
       <c r="U11" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="V11" t="n">
-        <v>6.55</v>
+        <v>6.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
@@ -1772,25 +1772,25 @@
         <v>1.24</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.42</v>
+        <v>3.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AC11" t="n">
         <v>3.15</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AG11" t="n">
         <v>1.69</v>
@@ -1849,16 +1849,16 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="M12" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="O12" t="n">
-        <v>3.72</v>
+        <v>3.65</v>
       </c>
       <c r="P12" t="n">
         <v>2.5</v>
@@ -1894,7 +1894,7 @@
         <v>5.25</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AB12" t="n">
         <v>2.62</v>
@@ -1903,10 +1903,10 @@
         <v>2.12</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="AF12" t="n">
         <v>2.6</v>
@@ -1915,7 +1915,7 @@
         <v>1.19</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46051.60416666666</v>
@@ -1968,61 +1968,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="M13" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="N13" t="n">
-        <v>3.2</v>
+        <v>3.63</v>
       </c>
       <c r="O13" t="n">
-        <v>3.46</v>
+        <v>3.58</v>
       </c>
       <c r="P13" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="R13" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="S13" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="T13" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="U13" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="V13" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="W13" t="n">
         <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Y13" t="n">
         <v>1.81</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AA13" t="n">
         <v>3.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AC13" t="n">
         <v>6.75</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AE13" t="n">
         <v>2.5</v>
@@ -2034,7 +2034,7 @@
         <v>1.46</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46051.625</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.15</v>
+        <v>1.74</v>
       </c>
       <c r="M14" t="n">
-        <v>3.2</v>
+        <v>2.87</v>
       </c>
       <c r="N14" t="n">
-        <v>2.9</v>
+        <v>5.1</v>
       </c>
       <c r="O14" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="P14" t="n">
-        <v>2.05</v>
+        <v>1.89</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.88</v>
+        <v>5.5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.39</v>
+        <v>1.55</v>
       </c>
       <c r="S14" t="n">
-        <v>2.73</v>
+        <v>2.2</v>
       </c>
       <c r="T14" t="n">
-        <v>2.84</v>
+        <v>3.8</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="V14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.25</v>
+        <v>2.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.93</v>
+        <v>2.74</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.85</v>
+        <v>1.35</v>
       </c>
       <c r="AC14" t="n">
-        <v>3</v>
+        <v>5.25</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.04</v>
+        <v>1.48</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.51</v>
+        <v>1.83</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46051.625</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.74</v>
+        <v>2.15</v>
       </c>
       <c r="M15" t="n">
-        <v>2.87</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>5.1</v>
+        <v>2.9</v>
       </c>
       <c r="O15" t="n">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="P15" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.41</v>
+        <v>3.88</v>
       </c>
       <c r="R15" t="n">
-        <v>1.65</v>
+        <v>1.39</v>
       </c>
       <c r="S15" t="n">
-        <v>2.1</v>
+        <v>2.73</v>
       </c>
       <c r="T15" t="n">
-        <v>3.8</v>
+        <v>2.84</v>
       </c>
       <c r="U15" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="V15" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.19</v>
+        <v>3.25</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.74</v>
+        <v>1.93</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.35</v>
+        <v>1.85</v>
       </c>
       <c r="AC15" t="n">
-        <v>5.4</v>
+        <v>3</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.09</v>
+        <v>1.28</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.44</v>
+        <v>2.04</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.83</v>
+        <v>1.51</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46051.625</v>
@@ -2444,19 +2444,19 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="M17" t="n">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
         <v>4.15</v>
       </c>
       <c r="O17" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="Q17" t="n">
         <v>4.5</v>
@@ -2465,52 +2465,52 @@
         <v>1.38</v>
       </c>
       <c r="S17" t="n">
-        <v>2.81</v>
+        <v>3.06</v>
       </c>
       <c r="T17" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="U17" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="V17" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
         <v>1.25</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA17" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AB17" t="n">
         <v>1.88</v>
       </c>
-      <c r="AB17" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AC17" t="n">
-        <v>2.85</v>
+        <v>3.22</v>
       </c>
       <c r="AD17" t="n">
         <v>1.33</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AF17" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH17" t="n">
         <v>2.04</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.95</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46051.83333333334</v>
@@ -2563,67 +2563,67 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="N18" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="O18" t="n">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="P18" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="Q18" t="n">
         <v>3.4</v>
       </c>
       <c r="R18" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="S18" t="n">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="T18" t="n">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="U18" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="V18" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="W18" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X18" t="n">
         <v>1.06</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="AA18" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AG18" t="n">
         <v>1.33</v>

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.91</v>
+        <v>5</v>
       </c>
       <c r="M6" t="n">
-        <v>2.5</v>
+        <v>4.66</v>
       </c>
       <c r="N6" t="n">
-        <v>2.64</v>
+        <v>1.53</v>
       </c>
       <c r="O6" t="n">
-        <v>4.15</v>
+        <v>4.6</v>
       </c>
       <c r="P6" t="n">
-        <v>1.64</v>
+        <v>2.62</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.4</v>
+        <v>1.84</v>
       </c>
       <c r="R6" t="n">
-        <v>1.78</v>
+        <v>1.16</v>
       </c>
       <c r="S6" t="n">
-        <v>2.11</v>
+        <v>4</v>
       </c>
       <c r="T6" t="n">
-        <v>4.55</v>
+        <v>1.95</v>
       </c>
       <c r="U6" t="n">
-        <v>1.18</v>
+        <v>1.75</v>
       </c>
       <c r="V6" t="n">
-        <v>11.5</v>
+        <v>4.1</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="X6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AH6" t="n">
         <v>1.12</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.28</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46051.5</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>5</v>
+        <v>2.91</v>
       </c>
       <c r="M7" t="n">
-        <v>4.66</v>
+        <v>2.5</v>
       </c>
       <c r="N7" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="O7" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AF7" t="n">
         <v>1.53</v>
       </c>
-      <c r="O7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="S7" t="n">
-        <v>4</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2.62</v>
-      </c>
       <c r="AG7" t="n">
-        <v>2.31</v>
+        <v>1.38</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46051.5</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="M13" t="n">
-        <v>2.45</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>3.63</v>
+        <v>2.9</v>
       </c>
       <c r="O13" t="n">
-        <v>3.58</v>
+        <v>2.8</v>
       </c>
       <c r="P13" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.4</v>
+        <v>3.76</v>
       </c>
       <c r="R13" t="n">
-        <v>1.83</v>
+        <v>1.36</v>
       </c>
       <c r="S13" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="T13" t="n">
-        <v>4.33</v>
+        <v>2.77</v>
       </c>
       <c r="U13" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="V13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="W13" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA13" t="n">
         <v>1.81</v>
       </c>
-      <c r="Z13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AB13" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD13" t="n">
         <v>1.33</v>
       </c>
-      <c r="AC13" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AE13" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.48</v>
+        <v>2</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46051.625</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.74</v>
+        <v>2.6</v>
       </c>
       <c r="M14" t="n">
-        <v>2.87</v>
+        <v>2.45</v>
       </c>
       <c r="N14" t="n">
-        <v>5.1</v>
+        <v>3.63</v>
       </c>
       <c r="O14" t="n">
-        <v>2.5</v>
+        <v>3.58</v>
       </c>
       <c r="P14" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="R14" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="S14" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="T14" t="n">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="U14" t="n">
         <v>1.18</v>
       </c>
       <c r="V14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.62</v>
+        <v>1.81</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.25</v>
+        <v>6.75</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AF14" t="n">
         <v>1.48</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.14</v>
+        <v>1.46</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.83</v>
+        <v>1.43</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46051.625</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.15</v>
+        <v>1.74</v>
       </c>
       <c r="M15" t="n">
-        <v>3.2</v>
+        <v>2.87</v>
       </c>
       <c r="N15" t="n">
-        <v>2.9</v>
+        <v>5.1</v>
       </c>
       <c r="O15" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="P15" t="n">
-        <v>2.05</v>
+        <v>1.89</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.88</v>
+        <v>5.5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.39</v>
+        <v>1.55</v>
       </c>
       <c r="S15" t="n">
-        <v>2.73</v>
+        <v>2.2</v>
       </c>
       <c r="T15" t="n">
-        <v>2.84</v>
+        <v>3.8</v>
       </c>
       <c r="U15" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="V15" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.25</v>
+        <v>2.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.93</v>
+        <v>2.74</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.85</v>
+        <v>1.35</v>
       </c>
       <c r="AC15" t="n">
-        <v>3</v>
+        <v>5.25</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.04</v>
+        <v>1.48</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.51</v>
+        <v>1.83</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46051.625</v>

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>3</v>
+      </c>
+      <c r="M11" t="n">
         <v>3.4</v>
       </c>
-      <c r="M11" t="n">
-        <v>3.2</v>
-      </c>
       <c r="N11" t="n">
-        <v>1.96</v>
+        <v>2.03</v>
       </c>
       <c r="O11" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P11" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="T11" t="n">
-        <v>2.73</v>
+        <v>2.13</v>
       </c>
       <c r="U11" t="n">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="V11" t="n">
-        <v>6.5</v>
+        <v>4.55</v>
       </c>
       <c r="W11" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.8</v>
+        <v>5.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.88</v>
+        <v>2.62</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.15</v>
+        <v>2.12</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.3</v>
+        <v>1.67</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.68</v>
+        <v>1.49</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.04</v>
+        <v>2.6</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.69</v>
+        <v>1.19</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46051.60416666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S12" t="n">
         <v>3</v>
       </c>
-      <c r="M12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N12" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="O12" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.9</v>
-      </c>
       <c r="T12" t="n">
-        <v>2.13</v>
+        <v>2.73</v>
       </c>
       <c r="U12" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="V12" t="n">
-        <v>4.55</v>
+        <v>6.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X12" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.09</v>
+        <v>1.24</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.25</v>
+        <v>3.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.62</v>
+        <v>1.88</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.12</v>
+        <v>3.15</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.67</v>
+        <v>1.3</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.49</v>
+        <v>1.68</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.6</v>
+        <v>2.04</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.19</v>
+        <v>1.69</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46051.60416666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2</v>
+        <v>2.45</v>
       </c>
       <c r="N13" t="n">
-        <v>2.9</v>
+        <v>3.63</v>
       </c>
       <c r="O13" t="n">
-        <v>2.8</v>
+        <v>3.58</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.76</v>
+        <v>4.4</v>
       </c>
       <c r="R13" t="n">
-        <v>1.36</v>
+        <v>1.83</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="T13" t="n">
-        <v>2.77</v>
+        <v>4.33</v>
       </c>
       <c r="U13" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="V13" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.3</v>
+        <v>1.81</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.25</v>
+        <v>2.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.81</v>
+        <v>3.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.79</v>
+        <v>1.33</v>
       </c>
       <c r="AC13" t="n">
-        <v>3</v>
+        <v>6.75</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="AF13" t="n">
-        <v>2</v>
+        <v>1.48</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46051.625</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="M14" t="n">
-        <v>2.45</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>3.63</v>
+        <v>2.9</v>
       </c>
       <c r="O14" t="n">
-        <v>3.58</v>
+        <v>2.8</v>
       </c>
       <c r="P14" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.4</v>
+        <v>3.76</v>
       </c>
       <c r="R14" t="n">
-        <v>1.83</v>
+        <v>1.36</v>
       </c>
       <c r="S14" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="T14" t="n">
-        <v>4.33</v>
+        <v>2.77</v>
       </c>
       <c r="U14" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="V14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X14" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA14" t="n">
         <v>1.81</v>
       </c>
-      <c r="Z14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AB14" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD14" t="n">
         <v>1.33</v>
       </c>
-      <c r="AC14" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AE14" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.48</v>
+        <v>2</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46051.625</v>

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5</v>
+        <v>2.91</v>
       </c>
       <c r="M6" t="n">
-        <v>4.66</v>
+        <v>2.5</v>
       </c>
       <c r="N6" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="O6" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AF6" t="n">
         <v>1.53</v>
       </c>
-      <c r="O6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>2.62</v>
-      </c>
       <c r="AG6" t="n">
-        <v>2.31</v>
+        <v>1.38</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46051.5</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.91</v>
+        <v>5</v>
       </c>
       <c r="M7" t="n">
-        <v>2.5</v>
+        <v>4.66</v>
       </c>
       <c r="N7" t="n">
-        <v>2.64</v>
+        <v>1.53</v>
       </c>
       <c r="O7" t="n">
-        <v>4.15</v>
+        <v>4.6</v>
       </c>
       <c r="P7" t="n">
-        <v>1.64</v>
+        <v>2.62</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.4</v>
+        <v>1.84</v>
       </c>
       <c r="R7" t="n">
-        <v>1.78</v>
+        <v>1.16</v>
       </c>
       <c r="S7" t="n">
-        <v>2.11</v>
+        <v>4</v>
       </c>
       <c r="T7" t="n">
-        <v>4.55</v>
+        <v>1.95</v>
       </c>
       <c r="U7" t="n">
-        <v>1.18</v>
+        <v>1.75</v>
       </c>
       <c r="V7" t="n">
-        <v>11.5</v>
+        <v>4.1</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="X7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AH7" t="n">
         <v>1.12</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.28</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46051.5</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S11" t="n">
         <v>3</v>
       </c>
-      <c r="M11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="O11" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.9</v>
-      </c>
       <c r="T11" t="n">
-        <v>2.13</v>
+        <v>2.73</v>
       </c>
       <c r="U11" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="V11" t="n">
-        <v>4.55</v>
+        <v>6.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.09</v>
+        <v>1.24</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.25</v>
+        <v>3.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.62</v>
+        <v>1.88</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.12</v>
+        <v>3.15</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.67</v>
+        <v>1.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.49</v>
+        <v>1.68</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.6</v>
+        <v>2.04</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.19</v>
+        <v>1.69</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46051.60416666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>3</v>
+      </c>
+      <c r="M12" t="n">
         <v>3.4</v>
       </c>
-      <c r="M12" t="n">
-        <v>3.2</v>
-      </c>
       <c r="N12" t="n">
-        <v>1.96</v>
+        <v>2.03</v>
       </c>
       <c r="O12" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P12" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="T12" t="n">
-        <v>2.73</v>
+        <v>2.13</v>
       </c>
       <c r="U12" t="n">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="V12" t="n">
-        <v>6.5</v>
+        <v>4.55</v>
       </c>
       <c r="W12" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.8</v>
+        <v>5.25</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.88</v>
+        <v>2.62</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.15</v>
+        <v>2.12</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.3</v>
+        <v>1.67</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.68</v>
+        <v>1.49</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.04</v>
+        <v>2.6</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.69</v>
+        <v>1.19</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46051.60416666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="M13" t="n">
-        <v>2.45</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>3.63</v>
+        <v>2.9</v>
       </c>
       <c r="O13" t="n">
-        <v>3.58</v>
+        <v>2.8</v>
       </c>
       <c r="P13" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.4</v>
+        <v>3.76</v>
       </c>
       <c r="R13" t="n">
-        <v>1.83</v>
+        <v>1.36</v>
       </c>
       <c r="S13" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="T13" t="n">
-        <v>4.33</v>
+        <v>2.77</v>
       </c>
       <c r="U13" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="V13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="W13" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA13" t="n">
         <v>1.81</v>
       </c>
-      <c r="Z13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AB13" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD13" t="n">
         <v>1.33</v>
       </c>
-      <c r="AC13" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AE13" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.48</v>
+        <v>2</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46051.625</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="M14" t="n">
-        <v>3.2</v>
+        <v>2.45</v>
       </c>
       <c r="N14" t="n">
-        <v>2.9</v>
+        <v>3.63</v>
       </c>
       <c r="O14" t="n">
-        <v>2.8</v>
+        <v>3.58</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.76</v>
+        <v>4.4</v>
       </c>
       <c r="R14" t="n">
-        <v>1.36</v>
+        <v>1.83</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="T14" t="n">
-        <v>2.77</v>
+        <v>4.33</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="V14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="W14" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>1.81</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.25</v>
+        <v>2.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.81</v>
+        <v>3.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.79</v>
+        <v>1.33</v>
       </c>
       <c r="AC14" t="n">
-        <v>3</v>
+        <v>6.75</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>1.48</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46051.625</v>

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.91</v>
+        <v>5</v>
       </c>
       <c r="M6" t="n">
-        <v>2.5</v>
+        <v>4.66</v>
       </c>
       <c r="N6" t="n">
-        <v>2.64</v>
+        <v>1.53</v>
       </c>
       <c r="O6" t="n">
-        <v>4.15</v>
+        <v>4.6</v>
       </c>
       <c r="P6" t="n">
-        <v>1.64</v>
+        <v>2.62</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.4</v>
+        <v>1.84</v>
       </c>
       <c r="R6" t="n">
-        <v>1.78</v>
+        <v>1.16</v>
       </c>
       <c r="S6" t="n">
-        <v>2.11</v>
+        <v>4</v>
       </c>
       <c r="T6" t="n">
-        <v>4.55</v>
+        <v>1.95</v>
       </c>
       <c r="U6" t="n">
-        <v>1.18</v>
+        <v>1.75</v>
       </c>
       <c r="V6" t="n">
-        <v>11.5</v>
+        <v>4.1</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="X6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AH6" t="n">
         <v>1.12</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.28</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46051.5</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>5</v>
+        <v>2.91</v>
       </c>
       <c r="M7" t="n">
-        <v>4.66</v>
+        <v>2.5</v>
       </c>
       <c r="N7" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="O7" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AF7" t="n">
         <v>1.53</v>
       </c>
-      <c r="O7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="S7" t="n">
-        <v>4</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2.62</v>
-      </c>
       <c r="AG7" t="n">
-        <v>2.31</v>
+        <v>1.38</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46051.5</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>3</v>
+      </c>
+      <c r="M11" t="n">
         <v>3.4</v>
       </c>
-      <c r="M11" t="n">
-        <v>3.2</v>
-      </c>
       <c r="N11" t="n">
-        <v>1.96</v>
+        <v>2.03</v>
       </c>
       <c r="O11" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P11" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="T11" t="n">
-        <v>2.73</v>
+        <v>2.13</v>
       </c>
       <c r="U11" t="n">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="V11" t="n">
-        <v>6.5</v>
+        <v>4.55</v>
       </c>
       <c r="W11" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.8</v>
+        <v>5.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.88</v>
+        <v>2.62</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.15</v>
+        <v>2.12</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.3</v>
+        <v>1.67</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.68</v>
+        <v>1.49</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.04</v>
+        <v>2.6</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.69</v>
+        <v>1.19</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46051.60416666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S12" t="n">
         <v>3</v>
       </c>
-      <c r="M12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N12" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="O12" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.9</v>
-      </c>
       <c r="T12" t="n">
-        <v>2.13</v>
+        <v>2.73</v>
       </c>
       <c r="U12" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="V12" t="n">
-        <v>4.55</v>
+        <v>6.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X12" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.09</v>
+        <v>1.24</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.25</v>
+        <v>3.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.62</v>
+        <v>1.88</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.12</v>
+        <v>3.15</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.67</v>
+        <v>1.3</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.49</v>
+        <v>1.68</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.6</v>
+        <v>2.04</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.19</v>
+        <v>1.69</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46051.60416666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.15</v>
+        <v>1.74</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2</v>
+        <v>2.87</v>
       </c>
       <c r="N13" t="n">
-        <v>2.9</v>
+        <v>5.1</v>
       </c>
       <c r="O13" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="P13" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S13" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q13" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3</v>
-      </c>
       <c r="T13" t="n">
-        <v>2.77</v>
+        <v>3.8</v>
       </c>
       <c r="U13" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="V13" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.25</v>
+        <v>2.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.81</v>
+        <v>2.74</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.79</v>
+        <v>1.35</v>
       </c>
       <c r="AC13" t="n">
-        <v>3</v>
+        <v>5.25</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="AF13" t="n">
-        <v>2</v>
+        <v>1.48</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46051.625</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.74</v>
+        <v>2.15</v>
       </c>
       <c r="M15" t="n">
-        <v>2.87</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>5.1</v>
+        <v>2.9</v>
       </c>
       <c r="O15" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="P15" t="n">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.5</v>
+        <v>3.76</v>
       </c>
       <c r="R15" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="T15" t="n">
-        <v>3.8</v>
+        <v>2.77</v>
       </c>
       <c r="U15" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="V15" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X15" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.74</v>
+        <v>1.81</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.35</v>
+        <v>1.79</v>
       </c>
       <c r="AC15" t="n">
-        <v>5.25</v>
+        <v>3</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.48</v>
+        <v>2</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46051.625</v>
@@ -2450,7 +2450,7 @@
         <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>4.15</v>
+        <v>4.4</v>
       </c>
       <c r="O17" t="n">
         <v>2.35</v>
@@ -2462,22 +2462,22 @@
         <v>4.5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>3.06</v>
+        <v>2.73</v>
       </c>
       <c r="T17" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="U17" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="V17" t="n">
         <v>6.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X17" t="n">
         <v>1.02</v>
@@ -2489,16 +2489,16 @@
         <v>3.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE17" t="n">
         <v>1.75</v>
@@ -2507,10 +2507,10 @@
         <v>1.94</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46051.83333333334</v>
@@ -2563,10 +2563,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="M18" t="n">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="N18" t="n">
         <v>2.9</v>
@@ -2584,31 +2584,31 @@
         <v>1.48</v>
       </c>
       <c r="S18" t="n">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="T18" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="U18" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="V18" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X18" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z18" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="AB18" t="n">
         <v>1.75</v>
@@ -2617,10 +2617,10 @@
         <v>3.44</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AF18" t="n">
         <v>1.95</v>

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5</v>
+        <v>2.91</v>
       </c>
       <c r="M6" t="n">
-        <v>4.66</v>
+        <v>2.5</v>
       </c>
       <c r="N6" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="O6" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AF6" t="n">
         <v>1.53</v>
       </c>
-      <c r="O6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>2.62</v>
-      </c>
       <c r="AG6" t="n">
-        <v>2.31</v>
+        <v>1.38</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46051.5</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.91</v>
+        <v>5</v>
       </c>
       <c r="M7" t="n">
-        <v>2.5</v>
+        <v>4.66</v>
       </c>
       <c r="N7" t="n">
-        <v>2.64</v>
+        <v>1.53</v>
       </c>
       <c r="O7" t="n">
-        <v>4.15</v>
+        <v>4.6</v>
       </c>
       <c r="P7" t="n">
-        <v>1.64</v>
+        <v>2.62</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.4</v>
+        <v>1.84</v>
       </c>
       <c r="R7" t="n">
-        <v>1.78</v>
+        <v>1.16</v>
       </c>
       <c r="S7" t="n">
-        <v>2.11</v>
+        <v>4</v>
       </c>
       <c r="T7" t="n">
-        <v>4.55</v>
+        <v>1.95</v>
       </c>
       <c r="U7" t="n">
-        <v>1.18</v>
+        <v>1.75</v>
       </c>
       <c r="V7" t="n">
-        <v>11.5</v>
+        <v>4.1</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="X7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AH7" t="n">
         <v>1.12</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.28</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46051.5</v>
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.74</v>
+        <v>2.6</v>
       </c>
       <c r="M13" t="n">
-        <v>2.87</v>
+        <v>2.45</v>
       </c>
       <c r="N13" t="n">
-        <v>5.1</v>
+        <v>3.63</v>
       </c>
       <c r="O13" t="n">
-        <v>2.5</v>
+        <v>3.58</v>
       </c>
       <c r="P13" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="R13" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="S13" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="T13" t="n">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="U13" t="n">
         <v>1.18</v>
       </c>
       <c r="V13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.62</v>
+        <v>1.81</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.25</v>
+        <v>6.75</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AF13" t="n">
         <v>1.48</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.14</v>
+        <v>1.46</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.83</v>
+        <v>1.43</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46051.625</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="M14" t="n">
-        <v>2.45</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>3.63</v>
+        <v>2.9</v>
       </c>
       <c r="O14" t="n">
-        <v>3.58</v>
+        <v>2.8</v>
       </c>
       <c r="P14" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.4</v>
+        <v>3.76</v>
       </c>
       <c r="R14" t="n">
-        <v>1.83</v>
+        <v>1.36</v>
       </c>
       <c r="S14" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="T14" t="n">
-        <v>4.33</v>
+        <v>2.77</v>
       </c>
       <c r="U14" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="V14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X14" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA14" t="n">
         <v>1.81</v>
       </c>
-      <c r="Z14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AB14" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD14" t="n">
         <v>1.33</v>
       </c>
-      <c r="AC14" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AE14" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.48</v>
+        <v>2</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46051.625</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.15</v>
+        <v>1.74</v>
       </c>
       <c r="M15" t="n">
-        <v>3.2</v>
+        <v>2.87</v>
       </c>
       <c r="N15" t="n">
-        <v>2.9</v>
+        <v>5.1</v>
       </c>
       <c r="O15" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="P15" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S15" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q15" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3</v>
-      </c>
       <c r="T15" t="n">
-        <v>2.77</v>
+        <v>3.8</v>
       </c>
       <c r="U15" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="V15" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="W15" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.25</v>
+        <v>2.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.81</v>
+        <v>2.74</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.79</v>
+        <v>1.35</v>
       </c>
       <c r="AC15" t="n">
-        <v>3</v>
+        <v>5.25</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="AF15" t="n">
-        <v>2</v>
+        <v>1.48</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46051.625</v>

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S11" t="n">
         <v>3</v>
       </c>
-      <c r="M11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="O11" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.9</v>
-      </c>
       <c r="T11" t="n">
-        <v>2.13</v>
+        <v>2.73</v>
       </c>
       <c r="U11" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="V11" t="n">
-        <v>4.55</v>
+        <v>6.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.09</v>
+        <v>1.24</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.25</v>
+        <v>3.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.62</v>
+        <v>1.88</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.12</v>
+        <v>3.15</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.67</v>
+        <v>1.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.49</v>
+        <v>1.68</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.6</v>
+        <v>2.04</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.19</v>
+        <v>1.69</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46051.60416666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>3</v>
+      </c>
+      <c r="M12" t="n">
         <v>3.4</v>
       </c>
-      <c r="M12" t="n">
-        <v>3.2</v>
-      </c>
       <c r="N12" t="n">
-        <v>1.96</v>
+        <v>2.03</v>
       </c>
       <c r="O12" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P12" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="T12" t="n">
-        <v>2.73</v>
+        <v>2.13</v>
       </c>
       <c r="U12" t="n">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="V12" t="n">
-        <v>6.5</v>
+        <v>4.55</v>
       </c>
       <c r="W12" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.8</v>
+        <v>5.25</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.88</v>
+        <v>2.62</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.15</v>
+        <v>2.12</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.3</v>
+        <v>1.67</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.68</v>
+        <v>1.49</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.04</v>
+        <v>2.6</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.69</v>
+        <v>1.19</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46051.60416666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.6</v>
+        <v>1.74</v>
       </c>
       <c r="M13" t="n">
-        <v>2.45</v>
+        <v>2.87</v>
       </c>
       <c r="N13" t="n">
-        <v>3.63</v>
+        <v>5.1</v>
       </c>
       <c r="O13" t="n">
-        <v>3.58</v>
+        <v>2.5</v>
       </c>
       <c r="P13" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="S13" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="T13" t="n">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="U13" t="n">
         <v>1.18</v>
       </c>
       <c r="V13" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="W13" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.81</v>
+        <v>1.62</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.1</v>
+        <v>2.74</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AC13" t="n">
-        <v>6.75</v>
+        <v>5.25</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AF13" t="n">
         <v>1.48</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.46</v>
+        <v>1.14</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.43</v>
+        <v>1.83</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46051.625</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="M14" t="n">
-        <v>3.2</v>
+        <v>2.45</v>
       </c>
       <c r="N14" t="n">
-        <v>2.9</v>
+        <v>3.63</v>
       </c>
       <c r="O14" t="n">
-        <v>2.8</v>
+        <v>3.58</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.76</v>
+        <v>4.4</v>
       </c>
       <c r="R14" t="n">
-        <v>1.36</v>
+        <v>1.83</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="T14" t="n">
-        <v>2.77</v>
+        <v>4.33</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="V14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="W14" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>1.81</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.25</v>
+        <v>2.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.81</v>
+        <v>3.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.79</v>
+        <v>1.33</v>
       </c>
       <c r="AC14" t="n">
-        <v>3</v>
+        <v>6.75</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>1.48</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46051.625</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.74</v>
+        <v>2.15</v>
       </c>
       <c r="M15" t="n">
-        <v>2.87</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>5.1</v>
+        <v>2.9</v>
       </c>
       <c r="O15" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="P15" t="n">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.5</v>
+        <v>3.76</v>
       </c>
       <c r="R15" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="T15" t="n">
-        <v>3.8</v>
+        <v>2.77</v>
       </c>
       <c r="U15" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="V15" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X15" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.74</v>
+        <v>1.81</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.35</v>
+        <v>1.79</v>
       </c>
       <c r="AC15" t="n">
-        <v>5.25</v>
+        <v>3</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.48</v>
+        <v>2</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46051.625</v>

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -662,70 +662,70 @@
         <v>2.5</v>
       </c>
       <c r="M2" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="N2" t="n">
-        <v>3.03</v>
+        <v>2.9</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46051.375</v>
@@ -784,67 +784,67 @@
         <v>3.5</v>
       </c>
       <c r="N3" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>5.69</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46051.41666666666</v>
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="M4" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N4" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46051.42708333334</v>
@@ -1016,19 +1016,19 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="M5" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="N5" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="O5" t="n">
         <v>4.55</v>
       </c>
       <c r="P5" t="n">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="Q5" t="n">
         <v>2</v>
@@ -1040,10 +1040,10 @@
         <v>4</v>
       </c>
       <c r="T5" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="U5" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="V5" t="n">
         <v>4.2</v>
@@ -1058,31 +1058,31 @@
         <v>1.06</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.15</v>
+        <v>6.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="AC5" t="n">
         <v>1.94</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.16</v>
+        <v>1.14</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46051.48958333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.91</v>
+        <v>4.8</v>
       </c>
       <c r="M6" t="n">
-        <v>2.5</v>
+        <v>4.8</v>
       </c>
       <c r="N6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="O6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P6" t="n">
         <v>2.64</v>
       </c>
-      <c r="O6" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.64</v>
-      </c>
       <c r="Q6" t="n">
-        <v>3.4</v>
+        <v>1.93</v>
       </c>
       <c r="R6" t="n">
-        <v>1.78</v>
+        <v>1.16</v>
       </c>
       <c r="S6" t="n">
-        <v>2.11</v>
+        <v>4.2</v>
       </c>
       <c r="T6" t="n">
-        <v>4.55</v>
+        <v>1.94</v>
       </c>
       <c r="U6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V6" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="W6" t="n">
         <v>1.18</v>
       </c>
-      <c r="V6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.02</v>
-      </c>
       <c r="X6" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.73</v>
+        <v>1.06</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.99</v>
+        <v>6.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.35</v>
+        <v>1.31</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.3</v>
+        <v>2.92</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.1</v>
+        <v>1.92</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.04</v>
+        <v>1.82</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.3</v>
+        <v>1.43</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.53</v>
+        <v>2.59</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.38</v>
+        <v>2.36</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46051.5</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>5</v>
+        <v>2.82</v>
       </c>
       <c r="M7" t="n">
-        <v>4.66</v>
+        <v>2.6</v>
       </c>
       <c r="N7" t="n">
-        <v>1.53</v>
+        <v>2.65</v>
       </c>
       <c r="O7" t="n">
-        <v>4.6</v>
+        <v>4.16</v>
       </c>
       <c r="P7" t="n">
-        <v>2.62</v>
+        <v>1.65</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.84</v>
+        <v>3.45</v>
       </c>
       <c r="R7" t="n">
-        <v>1.16</v>
+        <v>1.75</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>1.95</v>
       </c>
       <c r="T7" t="n">
-        <v>1.95</v>
+        <v>4.45</v>
       </c>
       <c r="U7" t="n">
-        <v>1.75</v>
+        <v>1.14</v>
       </c>
       <c r="V7" t="n">
-        <v>4.1</v>
+        <v>11</v>
       </c>
       <c r="W7" t="n">
-        <v>1.17</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.1</v>
+        <v>1.85</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.25</v>
+        <v>2.03</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.32</v>
+        <v>3.14</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.88</v>
+        <v>1.27</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.89</v>
+        <v>6.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.81</v>
+        <v>1.09</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.42</v>
+        <v>2.42</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.62</v>
+        <v>1.49</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.31</v>
+        <v>1.4</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46051.5</v>
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="M8" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="N8" t="n">
-        <v>3.68</v>
+        <v>3.65</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46051.52083333334</v>
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="M9" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="N9" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46051.54166666666</v>
@@ -1611,37 +1611,37 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="M10" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="N10" t="n">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="O10" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="P10" t="n">
-        <v>2.23</v>
+        <v>2.42</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.81</v>
+        <v>4.78</v>
       </c>
       <c r="R10" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S10" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="T10" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="U10" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="V10" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="W10" t="n">
         <v>1.07</v>
@@ -1650,34 +1650,34 @@
         <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.27</v>
+        <v>4.1</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46051.57291666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.4</v>
+        <v>3.11</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="N11" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="O11" t="n">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="P11" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.56</v>
+        <v>2.34</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="T11" t="n">
-        <v>2.73</v>
+        <v>2.15</v>
       </c>
       <c r="U11" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V11" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AA11" t="n">
         <v>1.44</v>
       </c>
-      <c r="V11" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AB11" t="n">
-        <v>1.88</v>
+        <v>2.62</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.15</v>
+        <v>2.12</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.3</v>
+        <v>1.64</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.68</v>
+        <v>1.4</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.04</v>
+        <v>2.62</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.69</v>
+        <v>1.2</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46051.60416666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>3.36</v>
       </c>
       <c r="N12" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="O12" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="P12" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.4</v>
+        <v>2.61</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="S12" t="n">
-        <v>3.9</v>
+        <v>2.88</v>
       </c>
       <c r="T12" t="n">
-        <v>2.13</v>
+        <v>2.66</v>
       </c>
       <c r="U12" t="n">
-        <v>1.63</v>
+        <v>1.39</v>
       </c>
       <c r="V12" t="n">
-        <v>4.55</v>
+        <v>6</v>
       </c>
       <c r="W12" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.25</v>
+        <v>3.42</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.5</v>
+        <v>1.86</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.62</v>
+        <v>1.87</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.12</v>
+        <v>3.15</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.67</v>
+        <v>1.29</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.49</v>
+        <v>1.68</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.6</v>
+        <v>2.04</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46051.60416666666</v>
@@ -1968,34 +1968,34 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.74</v>
+        <v>1.95</v>
       </c>
       <c r="M13" t="n">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="N13" t="n">
-        <v>5.1</v>
+        <v>4</v>
       </c>
       <c r="O13" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="P13" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.5</v>
+        <v>5.86</v>
       </c>
       <c r="R13" t="n">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="S13" t="n">
-        <v>2.2</v>
+        <v>1.99</v>
       </c>
       <c r="T13" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="U13" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="V13" t="n">
         <v>13</v>
@@ -2004,22 +2004,22 @@
         <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.62</v>
+        <v>1.88</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.74</v>
+        <v>3.25</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="AD13" t="n">
         <v>1.12</v>
@@ -2028,13 +2028,13 @@
         <v>2.4</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.14</v>
+        <v>1.37</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.83</v>
+        <v>1.64</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46051.625</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="M14" t="n">
-        <v>2.45</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>3.63</v>
+        <v>3.1</v>
       </c>
       <c r="O14" t="n">
-        <v>3.58</v>
+        <v>2.71</v>
       </c>
       <c r="P14" t="n">
-        <v>1.8</v>
+        <v>2.01</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="R14" t="n">
-        <v>1.83</v>
+        <v>1.42</v>
       </c>
       <c r="S14" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V14" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AA14" t="n">
         <v>2.05</v>
       </c>
-      <c r="T14" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V14" t="n">
-        <v>11</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AB14" t="n">
-        <v>1.33</v>
+        <v>1.77</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.75</v>
+        <v>3.34</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.04</v>
+        <v>1.24</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.5</v>
+        <v>1.78</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.48</v>
+        <v>1.93</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.43</v>
+        <v>1.68</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46051.625</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="M15" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="N15" t="n">
         <v>3.2</v>
       </c>
-      <c r="N15" t="n">
-        <v>2.9</v>
-      </c>
       <c r="O15" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2</v>
+        <v>1.76</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.76</v>
+        <v>4.35</v>
       </c>
       <c r="R15" t="n">
-        <v>1.36</v>
+        <v>1.83</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>1.87</v>
       </c>
       <c r="T15" t="n">
-        <v>2.77</v>
+        <v>4.5</v>
       </c>
       <c r="U15" t="n">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="V15" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="W15" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>1.81</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.25</v>
+        <v>2</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.81</v>
+        <v>3.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.79</v>
+        <v>1.26</v>
       </c>
       <c r="AC15" t="n">
-        <v>3</v>
+        <v>6.75</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="AF15" t="n">
-        <v>2</v>
+        <v>1.48</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46051.625</v>

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -665,7 +665,7 @@
         <v>2.7</v>
       </c>
       <c r="N2" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="O2" t="n">
         <v>3.42</v>
@@ -674,7 +674,7 @@
         <v>1.73</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.28</v>
+        <v>4.1</v>
       </c>
       <c r="R2" t="n">
         <v>1.69</v>
@@ -897,19 +897,19 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="M4" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N4" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="O4" t="n">
         <v>4.72</v>
       </c>
       <c r="P4" t="n">
-        <v>2.21</v>
+        <v>2.31</v>
       </c>
       <c r="Q4" t="n">
         <v>2.27</v>
@@ -927,7 +927,7 @@
         <v>1.41</v>
       </c>
       <c r="V4" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="W4" t="n">
         <v>1.05</v>
@@ -942,13 +942,13 @@
         <v>3.7</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AB4" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="AD4" t="n">
         <v>1.32</v>
@@ -960,7 +960,7 @@
         <v>2.01</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.19</v>
+        <v>1.95</v>
       </c>
       <c r="AH4" t="n">
         <v>1.16</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4.8</v>
+        <v>2.82</v>
       </c>
       <c r="M6" t="n">
-        <v>4.8</v>
+        <v>2.6</v>
       </c>
       <c r="N6" t="n">
-        <v>1.33</v>
+        <v>2.65</v>
       </c>
       <c r="O6" t="n">
-        <v>4.8</v>
+        <v>4.16</v>
       </c>
       <c r="P6" t="n">
-        <v>2.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.93</v>
+        <v>3.45</v>
       </c>
       <c r="R6" t="n">
-        <v>1.16</v>
+        <v>1.75</v>
       </c>
       <c r="S6" t="n">
-        <v>4.2</v>
+        <v>1.95</v>
       </c>
       <c r="T6" t="n">
-        <v>1.94</v>
+        <v>4.45</v>
       </c>
       <c r="U6" t="n">
-        <v>1.75</v>
+        <v>1.14</v>
       </c>
       <c r="V6" t="n">
-        <v>3.92</v>
+        <v>11</v>
       </c>
       <c r="W6" t="n">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.06</v>
+        <v>1.85</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.3</v>
+        <v>2.03</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.31</v>
+        <v>3.14</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.92</v>
+        <v>1.27</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.92</v>
+        <v>6.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.82</v>
+        <v>1.09</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.43</v>
+        <v>2.42</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.59</v>
+        <v>1.49</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.36</v>
+        <v>1.4</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.1</v>
+        <v>1.28</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46051.5</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.82</v>
+        <v>4.8</v>
       </c>
       <c r="M7" t="n">
-        <v>2.6</v>
+        <v>4.8</v>
       </c>
       <c r="N7" t="n">
-        <v>2.65</v>
+        <v>1.33</v>
       </c>
       <c r="O7" t="n">
-        <v>4.16</v>
+        <v>4.8</v>
       </c>
       <c r="P7" t="n">
-        <v>1.65</v>
+        <v>2.64</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.45</v>
+        <v>1.93</v>
       </c>
       <c r="R7" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U7" t="n">
         <v>1.75</v>
       </c>
-      <c r="S7" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="T7" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.14</v>
-      </c>
       <c r="V7" t="n">
-        <v>11</v>
+        <v>3.92</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="X7" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.85</v>
+        <v>1.06</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.03</v>
+        <v>6.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.14</v>
+        <v>1.31</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.27</v>
+        <v>2.92</v>
       </c>
       <c r="AC7" t="n">
-        <v>6.8</v>
+        <v>1.92</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.09</v>
+        <v>1.82</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.42</v>
+        <v>1.43</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.49</v>
+        <v>2.59</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.4</v>
+        <v>2.36</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46051.5</v>
@@ -1492,22 +1492,22 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="M9" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="N9" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="O9" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="P9" t="n">
         <v>2.32</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.78</v>
+        <v>4.67</v>
       </c>
       <c r="R9" t="n">
         <v>1.27</v>
@@ -1531,7 +1531,7 @@
         <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z9" t="n">
         <v>4.3</v>
@@ -1540,7 +1540,7 @@
         <v>1.59</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="AC9" t="n">
         <v>2.43</v>
@@ -1558,7 +1558,7 @@
         <v>1.17</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46051.54166666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.11</v>
+        <v>3.4</v>
       </c>
       <c r="M11" t="n">
-        <v>3.8</v>
+        <v>3.36</v>
       </c>
       <c r="N11" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="O11" t="n">
-        <v>3.64</v>
+        <v>3.75</v>
       </c>
       <c r="P11" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.34</v>
+        <v>2.61</v>
       </c>
       <c r="R11" t="n">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="S11" t="n">
-        <v>3.55</v>
+        <v>2.88</v>
       </c>
       <c r="T11" t="n">
-        <v>2.15</v>
+        <v>2.66</v>
       </c>
       <c r="U11" t="n">
-        <v>1.56</v>
+        <v>1.39</v>
       </c>
       <c r="V11" t="n">
-        <v>4.55</v>
+        <v>6</v>
       </c>
       <c r="W11" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.25</v>
+        <v>3.42</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.44</v>
+        <v>1.86</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.62</v>
+        <v>1.87</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.12</v>
+        <v>3.15</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.64</v>
+        <v>1.29</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.4</v>
+        <v>1.68</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.62</v>
+        <v>2.04</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46051.60416666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.4</v>
+        <v>3.11</v>
       </c>
       <c r="M12" t="n">
-        <v>3.36</v>
+        <v>3.8</v>
       </c>
       <c r="N12" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="O12" t="n">
-        <v>3.75</v>
+        <v>3.64</v>
       </c>
       <c r="P12" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.61</v>
+        <v>2.34</v>
       </c>
       <c r="R12" t="n">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="S12" t="n">
-        <v>2.88</v>
+        <v>3.55</v>
       </c>
       <c r="T12" t="n">
-        <v>2.66</v>
+        <v>2.15</v>
       </c>
       <c r="U12" t="n">
-        <v>1.39</v>
+        <v>1.56</v>
       </c>
       <c r="V12" t="n">
-        <v>6</v>
+        <v>4.55</v>
       </c>
       <c r="W12" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.42</v>
+        <v>5.25</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.86</v>
+        <v>1.44</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.87</v>
+        <v>2.62</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.15</v>
+        <v>2.12</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.29</v>
+        <v>1.64</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.68</v>
+        <v>1.4</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.04</v>
+        <v>2.62</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46051.60416666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="M13" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="O13" t="n">
-        <v>2.55</v>
+        <v>2.71</v>
       </c>
       <c r="P13" t="n">
-        <v>1.7</v>
+        <v>2.01</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.86</v>
+        <v>4.3</v>
       </c>
       <c r="R13" t="n">
-        <v>1.72</v>
+        <v>1.42</v>
       </c>
       <c r="S13" t="n">
-        <v>1.99</v>
+        <v>2.62</v>
       </c>
       <c r="T13" t="n">
-        <v>3.85</v>
+        <v>3.01</v>
       </c>
       <c r="U13" t="n">
-        <v>1.17</v>
+        <v>1.35</v>
       </c>
       <c r="V13" t="n">
-        <v>13</v>
+        <v>7.3</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.88</v>
+        <v>1.32</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.01</v>
+        <v>3.28</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.25</v>
+        <v>2.05</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.33</v>
+        <v>1.77</v>
       </c>
       <c r="AC13" t="n">
-        <v>6</v>
+        <v>3.34</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.4</v>
+        <v>1.78</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.5</v>
+        <v>1.93</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46051.625</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="M14" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="N14" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="O14" t="n">
-        <v>2.71</v>
+        <v>2.55</v>
       </c>
       <c r="P14" t="n">
-        <v>2.01</v>
+        <v>1.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.3</v>
+        <v>5.86</v>
       </c>
       <c r="R14" t="n">
-        <v>1.42</v>
+        <v>1.72</v>
       </c>
       <c r="S14" t="n">
-        <v>2.62</v>
+        <v>1.99</v>
       </c>
       <c r="T14" t="n">
-        <v>3.01</v>
+        <v>3.85</v>
       </c>
       <c r="U14" t="n">
-        <v>1.35</v>
+        <v>1.17</v>
       </c>
       <c r="V14" t="n">
-        <v>7.3</v>
+        <v>13</v>
       </c>
       <c r="W14" t="n">
         <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.32</v>
+        <v>1.88</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.28</v>
+        <v>2.01</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.05</v>
+        <v>3.25</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.77</v>
+        <v>1.33</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.34</v>
+        <v>6</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.78</v>
+        <v>2.4</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.93</v>
+        <v>1.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46051.625</v>

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -906,13 +906,13 @@
         <v>1.7</v>
       </c>
       <c r="O4" t="n">
-        <v>4.72</v>
+        <v>4.45</v>
       </c>
       <c r="P4" t="n">
         <v>2.31</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.27</v>
+        <v>2.34</v>
       </c>
       <c r="R4" t="n">
         <v>1.31</v>
@@ -933,13 +933,13 @@
         <v>1.05</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
         <v>1.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="AA4" t="n">
         <v>1.76</v>
@@ -1135,34 +1135,34 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.82</v>
+        <v>2.91</v>
       </c>
       <c r="M6" t="n">
         <v>2.6</v>
       </c>
       <c r="N6" t="n">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="O6" t="n">
-        <v>4.16</v>
+        <v>4.45</v>
       </c>
       <c r="P6" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="R6" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="S6" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="T6" t="n">
-        <v>4.45</v>
+        <v>3.85</v>
       </c>
       <c r="U6" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="V6" t="n">
         <v>11</v>
@@ -1171,34 +1171,34 @@
         <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.85</v>
+        <v>1.69</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.03</v>
+        <v>2.11</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.14</v>
+        <v>3.27</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AC6" t="n">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AH6" t="n">
         <v>1.28</v>
@@ -1254,40 +1254,40 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.8</v>
+        <v>4.78</v>
       </c>
       <c r="M7" t="n">
-        <v>4.8</v>
+        <v>4.55</v>
       </c>
       <c r="N7" t="n">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="O7" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="P7" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="R7" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="S7" t="n">
         <v>4.2</v>
       </c>
       <c r="T7" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="U7" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="V7" t="n">
-        <v>3.92</v>
+        <v>4.1</v>
       </c>
       <c r="W7" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X7" t="n">
         <v>1.01</v>
@@ -1296,31 +1296,31 @@
         <v>1.06</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AD7" t="n">
         <v>1.82</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.36</v>
+        <v>1.12</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46051.5</v>
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="M9" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="N9" t="n">
         <v>4.33</v>
@@ -1504,10 +1504,10 @@
         <v>2.17</v>
       </c>
       <c r="P9" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.67</v>
+        <v>4.72</v>
       </c>
       <c r="R9" t="n">
         <v>1.27</v>
@@ -1522,7 +1522,7 @@
         <v>1.5</v>
       </c>
       <c r="V9" t="n">
-        <v>5.3</v>
+        <v>5.35</v>
       </c>
       <c r="W9" t="n">
         <v>1.09</v>
@@ -1531,28 +1531,28 @@
         <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z9" t="n">
         <v>4.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="AB9" t="n">
         <v>2.24</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.43</v>
+        <v>2.28</v>
       </c>
       <c r="AD9" t="n">
         <v>1.44</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AG9" t="n">
         <v>1.17</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.4</v>
+        <v>3.02</v>
       </c>
       <c r="M11" t="n">
-        <v>3.36</v>
+        <v>3.7</v>
       </c>
       <c r="N11" t="n">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="O11" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="P11" t="n">
-        <v>2.1</v>
+        <v>2.56</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.61</v>
+        <v>2.52</v>
       </c>
       <c r="R11" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="S11" t="n">
-        <v>2.88</v>
+        <v>3.58</v>
       </c>
       <c r="T11" t="n">
-        <v>2.66</v>
+        <v>2.15</v>
       </c>
       <c r="U11" t="n">
-        <v>1.39</v>
+        <v>1.67</v>
       </c>
       <c r="V11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.42</v>
+        <v>5.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.86</v>
+        <v>1.41</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.87</v>
+        <v>2.52</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.15</v>
+        <v>2.09</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.29</v>
+        <v>1.66</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.68</v>
+        <v>1.39</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.04</v>
+        <v>2.65</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.24</v>
+        <v>1.65</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46051.60416666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.11</v>
+        <v>3.4</v>
       </c>
       <c r="M12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V12" t="n">
+        <v>6</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z12" t="n">
         <v>3.8</v>
       </c>
-      <c r="N12" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="O12" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V12" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>5.25</v>
-      </c>
       <c r="AA12" t="n">
-        <v>1.44</v>
+        <v>1.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.62</v>
+        <v>1.92</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.12</v>
+        <v>3.04</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.64</v>
+        <v>1.34</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.62</v>
+        <v>2.05</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46051.60416666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="N13" t="n">
-        <v>3.1</v>
+        <v>4.33</v>
       </c>
       <c r="O13" t="n">
-        <v>2.71</v>
+        <v>2.9</v>
       </c>
       <c r="P13" t="n">
-        <v>2.01</v>
+        <v>1.83</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.42</v>
+        <v>1.72</v>
       </c>
       <c r="S13" t="n">
-        <v>2.62</v>
+        <v>1.99</v>
       </c>
       <c r="T13" t="n">
-        <v>3.01</v>
+        <v>3.85</v>
       </c>
       <c r="U13" t="n">
-        <v>1.35</v>
+        <v>1.17</v>
       </c>
       <c r="V13" t="n">
-        <v>7.3</v>
+        <v>13</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.32</v>
+        <v>1.64</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.28</v>
+        <v>2.12</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.05</v>
+        <v>3.08</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.77</v>
+        <v>1.38</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.34</v>
+        <v>5.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.78</v>
+        <v>2.4</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.93</v>
+        <v>1.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46051.625</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.95</v>
+        <v>2.49</v>
       </c>
       <c r="M14" t="n">
-        <v>2.8</v>
+        <v>2.37</v>
       </c>
       <c r="N14" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="O14" t="n">
-        <v>2.55</v>
+        <v>3.6</v>
       </c>
       <c r="P14" t="n">
-        <v>1.7</v>
+        <v>1.59</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.86</v>
+        <v>5.05</v>
       </c>
       <c r="R14" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="S14" t="n">
-        <v>1.99</v>
+        <v>1.88</v>
       </c>
       <c r="T14" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="U14" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="V14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AC14" t="n">
-        <v>6</v>
+        <v>6.75</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.64</v>
+        <v>1.42</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46051.625</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="M15" t="n">
-        <v>2.45</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="O15" t="n">
-        <v>3.4</v>
+        <v>2.71</v>
       </c>
       <c r="P15" t="n">
-        <v>1.76</v>
+        <v>2.01</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.35</v>
+        <v>4.3</v>
       </c>
       <c r="R15" t="n">
-        <v>1.83</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
-        <v>1.87</v>
+        <v>2.62</v>
       </c>
       <c r="T15" t="n">
-        <v>4.5</v>
+        <v>3.01</v>
       </c>
       <c r="U15" t="n">
-        <v>1.13</v>
+        <v>1.35</v>
       </c>
       <c r="V15" t="n">
-        <v>11</v>
+        <v>7.3</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.81</v>
+        <v>1.32</v>
       </c>
       <c r="Z15" t="n">
-        <v>2</v>
+        <v>3.28</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.26</v>
+        <v>1.77</v>
       </c>
       <c r="AC15" t="n">
-        <v>6.75</v>
+        <v>3.34</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.04</v>
+        <v>1.24</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.5</v>
+        <v>1.78</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.48</v>
+        <v>1.93</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.42</v>
+        <v>1.68</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46051.625</v>
@@ -2334,64 +2334,64 @@
         <v>1.82</v>
       </c>
       <c r="O16" t="n">
-        <v>5.23</v>
+        <v>4.05</v>
       </c>
       <c r="P16" t="n">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.51</v>
+        <v>2.64</v>
       </c>
       <c r="R16" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S16" t="n">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="T16" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="U16" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V16" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="W16" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X16" t="n">
         <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.97</v>
+        <v>2.87</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.5</v>
+        <v>3.72</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46051.70833333334</v>
@@ -2444,37 +2444,37 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="M17" t="n">
         <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="O17" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="P17" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="R17" t="n">
         <v>1.4</v>
       </c>
       <c r="S17" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T17" t="n">
         <v>2.73</v>
       </c>
-      <c r="T17" t="n">
-        <v>2.69</v>
-      </c>
       <c r="U17" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V17" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="W17" t="n">
         <v>1.08</v>
@@ -2483,19 +2483,19 @@
         <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AB17" t="n">
         <v>1.85</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AD17" t="n">
         <v>1.3</v>
@@ -2507,10 +2507,10 @@
         <v>1.94</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46051.83333333334</v>
@@ -2563,70 +2563,70 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="M18" t="n">
         <v>3.1</v>
       </c>
       <c r="N18" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="O18" t="n">
         <v>2.9</v>
       </c>
-      <c r="O18" t="n">
-        <v>3.05</v>
-      </c>
       <c r="P18" t="n">
-        <v>2.11</v>
+        <v>1.99</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.4</v>
+        <v>3.59</v>
       </c>
       <c r="R18" t="n">
         <v>1.48</v>
       </c>
       <c r="S18" t="n">
-        <v>2.47</v>
+        <v>2.84</v>
       </c>
       <c r="T18" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="U18" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="V18" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="W18" t="n">
         <v>1.03</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z18" t="n">
         <v>2.94</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.44</v>
+        <v>3.59</v>
       </c>
       <c r="AD18" t="n">
         <v>1.25</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AF18" t="n">
         <v>1.95</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AH18" t="n">
         <v>1.5</v>

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -662,7 +662,7 @@
         <v>2.5</v>
       </c>
       <c r="M2" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="N2" t="n">
         <v>3</v>
@@ -698,7 +698,7 @@
         <v>1.11</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="Z2" t="n">
         <v>1.99</v>
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4.75</v>
+        <v>5.35</v>
       </c>
       <c r="M3" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N3" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="O3" t="n">
-        <v>5.69</v>
+        <v>6.6</v>
       </c>
       <c r="P3" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="R3" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S3" t="n">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="T3" t="n">
-        <v>2.97</v>
+        <v>2.75</v>
       </c>
       <c r="U3" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="V3" t="n">
-        <v>7.8</v>
+        <v>6.7</v>
       </c>
       <c r="W3" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X3" t="n">
         <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.68</v>
+        <v>3.08</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46051.41666666666</v>
@@ -912,7 +912,7 @@
         <v>2.31</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="R4" t="n">
         <v>1.31</v>
@@ -951,7 +951,7 @@
         <v>2.88</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AE4" t="n">
         <v>1.7</v>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="M5" t="n">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="N5" t="n">
         <v>1.6</v>
@@ -1028,7 +1028,7 @@
         <v>4.55</v>
       </c>
       <c r="P5" t="n">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="Q5" t="n">
         <v>2</v>
@@ -1040,10 +1040,10 @@
         <v>4</v>
       </c>
       <c r="T5" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="V5" t="n">
         <v>4.2</v>
@@ -1055,31 +1055,31 @@
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.2</v>
+        <v>6.15</v>
       </c>
       <c r="AA5" t="n">
         <v>1.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="AC5" t="n">
         <v>1.94</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AH5" t="n">
         <v>1.14</v>
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.91</v>
+        <v>3.2</v>
       </c>
       <c r="M6" t="n">
         <v>2.6</v>
       </c>
       <c r="N6" t="n">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="O6" t="n">
         <v>4.45</v>
@@ -1162,13 +1162,13 @@
         <v>3.85</v>
       </c>
       <c r="U6" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="V6" t="n">
         <v>11</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
         <v>1.11</v>
@@ -1192,7 +1192,7 @@
         <v>1.05</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AF6" t="n">
         <v>1.5</v>
@@ -1257,16 +1257,16 @@
         <v>4.78</v>
       </c>
       <c r="M7" t="n">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="N7" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="O7" t="n">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="P7" t="n">
-        <v>2.65</v>
+        <v>2.76</v>
       </c>
       <c r="Q7" t="n">
         <v>1.89</v>
@@ -1275,19 +1275,19 @@
         <v>1.17</v>
       </c>
       <c r="S7" t="n">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="T7" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="U7" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="V7" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="W7" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X7" t="n">
         <v>1.01</v>
@@ -1305,19 +1305,19 @@
         <v>2.85</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AE7" t="n">
         <v>1.4</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AH7" t="n">
         <v>1.11</v>
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="M8" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="N8" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O8" t="n">
-        <v>2.61</v>
+        <v>2.38</v>
       </c>
       <c r="P8" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.45</v>
+        <v>5.32</v>
       </c>
       <c r="R8" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S8" t="n">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="T8" t="n">
-        <v>2.88</v>
+        <v>3.13</v>
       </c>
       <c r="U8" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V8" t="n">
-        <v>7.4</v>
+        <v>8.1</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.97</v>
+        <v>2.78</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.5</v>
+        <v>3.84</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AG8" t="n">
         <v>1.26</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46051.52083333334</v>
@@ -1492,22 +1492,22 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="M9" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="N9" t="n">
         <v>4.33</v>
       </c>
       <c r="O9" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="P9" t="n">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.72</v>
+        <v>4.64</v>
       </c>
       <c r="R9" t="n">
         <v>1.27</v>
@@ -1531,16 +1531,16 @@
         <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z9" t="n">
         <v>4.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.24</v>
+        <v>2.19</v>
       </c>
       <c r="AC9" t="n">
         <v>2.28</v>
@@ -1549,16 +1549,16 @@
         <v>1.44</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46051.54166666666</v>
@@ -1611,43 +1611,43 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="M10" t="n">
         <v>3.6</v>
       </c>
       <c r="N10" t="n">
-        <v>3.9</v>
+        <v>4.15</v>
       </c>
       <c r="O10" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="P10" t="n">
-        <v>2.42</v>
+        <v>2.21</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.78</v>
+        <v>4.66</v>
       </c>
       <c r="R10" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="S10" t="n">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="T10" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="U10" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="V10" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="W10" t="n">
         <v>1.07</v>
       </c>
       <c r="X10" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
         <v>1.21</v>
@@ -1656,28 +1656,28 @@
         <v>4.1</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AD10" t="n">
         <v>1.39</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46051.57291666666</v>
@@ -1730,22 +1730,22 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.02</v>
+        <v>2.92</v>
       </c>
       <c r="M11" t="n">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="N11" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O11" t="n">
-        <v>3.55</v>
+        <v>3.44</v>
       </c>
       <c r="P11" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="R11" t="n">
         <v>1.25</v>
@@ -1760,7 +1760,7 @@
         <v>1.67</v>
       </c>
       <c r="V11" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="W11" t="n">
         <v>1.17</v>
@@ -1772,13 +1772,13 @@
         <v>1.13</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.3</v>
+        <v>5.35</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="AC11" t="n">
         <v>2.09</v>
@@ -1793,10 +1793,10 @@
         <v>2.65</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46051.60416666666</v>
@@ -1855,7 +1855,7 @@
         <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="O12" t="n">
         <v>3.6</v>
@@ -1867,22 +1867,22 @@
         <v>2.61</v>
       </c>
       <c r="R12" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="T12" t="n">
         <v>2.65</v>
       </c>
       <c r="U12" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V12" t="n">
-        <v>6</v>
+        <v>6.55</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
@@ -1891,13 +1891,13 @@
         <v>1.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.8</v>
+        <v>3.42</v>
       </c>
       <c r="AA12" t="n">
         <v>1.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AC12" t="n">
         <v>3.04</v>
@@ -1906,7 +1906,7 @@
         <v>1.34</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AF12" t="n">
         <v>2.05</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="M13" t="n">
-        <v>2.75</v>
+        <v>3.35</v>
       </c>
       <c r="N13" t="n">
-        <v>4.33</v>
+        <v>3.3</v>
       </c>
       <c r="O13" t="n">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="P13" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="R13" t="n">
-        <v>1.72</v>
+        <v>1.42</v>
       </c>
       <c r="S13" t="n">
-        <v>1.99</v>
+        <v>2.62</v>
       </c>
       <c r="T13" t="n">
-        <v>3.85</v>
+        <v>2.65</v>
       </c>
       <c r="U13" t="n">
-        <v>1.17</v>
+        <v>1.35</v>
       </c>
       <c r="V13" t="n">
-        <v>13</v>
+        <v>7.3</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.64</v>
+        <v>1.24</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.12</v>
+        <v>3.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.08</v>
+        <v>1.81</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.38</v>
+        <v>1.79</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.6</v>
+        <v>3</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.4</v>
+        <v>1.78</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.5</v>
+        <v>1.93</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46051.625</v>
@@ -2090,7 +2090,7 @@
         <v>2.49</v>
       </c>
       <c r="M14" t="n">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="N14" t="n">
         <v>3.3</v>
@@ -2114,7 +2114,7 @@
         <v>4.4</v>
       </c>
       <c r="U14" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="V14" t="n">
         <v>11</v>
@@ -2123,19 +2123,19 @@
         <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AA14" t="n">
         <v>3.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AC14" t="n">
         <v>6.75</v>
@@ -2150,10 +2150,10 @@
         <v>1.48</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46051.625</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="N15" t="n">
-        <v>3.1</v>
+        <v>4.33</v>
       </c>
       <c r="O15" t="n">
-        <v>2.71</v>
+        <v>2.9</v>
       </c>
       <c r="P15" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>1.72</v>
       </c>
       <c r="S15" t="n">
-        <v>2.62</v>
+        <v>1.99</v>
       </c>
       <c r="T15" t="n">
-        <v>3.01</v>
+        <v>3.85</v>
       </c>
       <c r="U15" t="n">
-        <v>1.35</v>
+        <v>1.17</v>
       </c>
       <c r="V15" t="n">
-        <v>7.3</v>
+        <v>13</v>
       </c>
       <c r="W15" t="n">
         <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.32</v>
+        <v>1.64</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.28</v>
+        <v>2.12</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.05</v>
+        <v>2.83</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.77</v>
+        <v>1.37</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.34</v>
+        <v>5.55</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.78</v>
+        <v>2.4</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.93</v>
+        <v>1.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46051.625</v>

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.92</v>
+        <v>3.4</v>
       </c>
       <c r="M11" t="n">
-        <v>3.68</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="O11" t="n">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="P11" t="n">
-        <v>2.57</v>
+        <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.55</v>
+        <v>2.61</v>
       </c>
       <c r="R11" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="S11" t="n">
-        <v>3.58</v>
+        <v>2.88</v>
       </c>
       <c r="T11" t="n">
-        <v>2.15</v>
+        <v>2.65</v>
       </c>
       <c r="U11" t="n">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="V11" t="n">
-        <v>4.9</v>
+        <v>6.55</v>
       </c>
       <c r="W11" t="n">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.35</v>
+        <v>3.42</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.4</v>
+        <v>1.85</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.56</v>
+        <v>1.95</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.09</v>
+        <v>3.04</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.66</v>
+        <v>1.34</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.39</v>
+        <v>1.68</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.65</v>
+        <v>2.05</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.62</v>
+        <v>1.27</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46051.60416666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.4</v>
+        <v>2.92</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>3.68</v>
       </c>
       <c r="N12" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="O12" t="n">
-        <v>3.6</v>
+        <v>3.44</v>
       </c>
       <c r="P12" t="n">
-        <v>2.1</v>
+        <v>2.57</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.61</v>
+        <v>2.55</v>
       </c>
       <c r="R12" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="S12" t="n">
-        <v>2.88</v>
+        <v>3.58</v>
       </c>
       <c r="T12" t="n">
-        <v>2.65</v>
+        <v>2.15</v>
       </c>
       <c r="U12" t="n">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="V12" t="n">
-        <v>6.55</v>
+        <v>4.9</v>
       </c>
       <c r="W12" t="n">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.42</v>
+        <v>5.35</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.95</v>
+        <v>2.56</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.04</v>
+        <v>2.09</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.34</v>
+        <v>1.66</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.68</v>
+        <v>1.39</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.05</v>
+        <v>2.65</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.27</v>
+        <v>1.62</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46051.60416666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="M13" t="n">
-        <v>3.35</v>
+        <v>2.88</v>
       </c>
       <c r="N13" t="n">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="O13" t="n">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="P13" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.42</v>
+        <v>1.72</v>
       </c>
       <c r="S13" t="n">
-        <v>2.62</v>
+        <v>1.99</v>
       </c>
       <c r="T13" t="n">
-        <v>2.65</v>
+        <v>3.85</v>
       </c>
       <c r="U13" t="n">
-        <v>1.35</v>
+        <v>1.17</v>
       </c>
       <c r="V13" t="n">
-        <v>7.3</v>
+        <v>13</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.24</v>
+        <v>1.64</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.25</v>
+        <v>2.12</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.81</v>
+        <v>2.83</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.79</v>
+        <v>1.37</v>
       </c>
       <c r="AC13" t="n">
-        <v>3</v>
+        <v>5.55</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.29</v>
+        <v>1.08</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.78</v>
+        <v>2.4</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.93</v>
+        <v>1.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46051.625</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="M15" t="n">
-        <v>2.88</v>
+        <v>3.35</v>
       </c>
       <c r="N15" t="n">
-        <v>4.33</v>
+        <v>3.3</v>
       </c>
       <c r="O15" t="n">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="P15" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="R15" t="n">
-        <v>1.72</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
-        <v>1.99</v>
+        <v>2.62</v>
       </c>
       <c r="T15" t="n">
-        <v>3.85</v>
+        <v>2.65</v>
       </c>
       <c r="U15" t="n">
-        <v>1.17</v>
+        <v>1.35</v>
       </c>
       <c r="V15" t="n">
-        <v>13</v>
+        <v>7.3</v>
       </c>
       <c r="W15" t="n">
         <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.64</v>
+        <v>1.24</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.12</v>
+        <v>3.25</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.83</v>
+        <v>1.81</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.37</v>
+        <v>1.79</v>
       </c>
       <c r="AC15" t="n">
-        <v>5.55</v>
+        <v>3</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.4</v>
+        <v>1.78</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.5</v>
+        <v>1.93</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46051.625</v>
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.33</v>
+        <v>3.68</v>
       </c>
       <c r="M16" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="O16" t="n">
-        <v>4.05</v>
+        <v>4.5</v>
       </c>
       <c r="P16" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="R16" t="n">
         <v>1.42</v>
       </c>
       <c r="S16" t="n">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="T16" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="U16" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V16" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="W16" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
         <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.87</v>
+        <v>3.07</v>
       </c>
       <c r="AA16" t="n">
         <v>2.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.72</v>
+        <v>3.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AG16" t="n">
         <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46051.70833333334</v>

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI18"/>
+  <dimension ref="A1:AI19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.4</v>
+        <v>2.92</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>3.68</v>
       </c>
       <c r="N11" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="O11" t="n">
-        <v>3.6</v>
+        <v>3.44</v>
       </c>
       <c r="P11" t="n">
-        <v>2.1</v>
+        <v>2.57</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.61</v>
+        <v>2.55</v>
       </c>
       <c r="R11" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="S11" t="n">
-        <v>2.88</v>
+        <v>3.58</v>
       </c>
       <c r="T11" t="n">
-        <v>2.65</v>
+        <v>2.15</v>
       </c>
       <c r="U11" t="n">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="V11" t="n">
-        <v>6.55</v>
+        <v>4.9</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.42</v>
+        <v>5.35</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.95</v>
+        <v>2.56</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.04</v>
+        <v>2.09</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.34</v>
+        <v>1.66</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.68</v>
+        <v>1.39</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.05</v>
+        <v>2.65</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.27</v>
+        <v>1.62</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46051.60416666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.92</v>
+        <v>3.4</v>
       </c>
       <c r="M12" t="n">
-        <v>3.68</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="O12" t="n">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="P12" t="n">
-        <v>2.57</v>
+        <v>2.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.55</v>
+        <v>2.61</v>
       </c>
       <c r="R12" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="S12" t="n">
-        <v>3.58</v>
+        <v>2.88</v>
       </c>
       <c r="T12" t="n">
-        <v>2.15</v>
+        <v>2.65</v>
       </c>
       <c r="U12" t="n">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="V12" t="n">
-        <v>4.9</v>
+        <v>6.55</v>
       </c>
       <c r="W12" t="n">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.35</v>
+        <v>3.42</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.4</v>
+        <v>1.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.56</v>
+        <v>1.95</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.09</v>
+        <v>3.04</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.66</v>
+        <v>1.34</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.39</v>
+        <v>1.68</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.65</v>
+        <v>2.05</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.62</v>
+        <v>1.27</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46051.60416666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2321,65 +2321,65 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.68</v>
+        <v>1.44</v>
       </c>
       <c r="M16" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>1.9</v>
+        <v>6</v>
       </c>
       <c r="O16" t="n">
-        <v>4.5</v>
+        <v>1.79</v>
       </c>
       <c r="P16" t="n">
-        <v>2.05</v>
+        <v>2.24</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.6</v>
+        <v>6.38</v>
       </c>
       <c r="R16" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="S16" t="n">
-        <v>2.53</v>
+        <v>3.08</v>
       </c>
       <c r="T16" t="n">
-        <v>2.88</v>
+        <v>2.49</v>
       </c>
       <c r="U16" t="n">
-        <v>1.32</v>
+        <v>1.46</v>
       </c>
       <c r="V16" t="n">
-        <v>7.4</v>
+        <v>5.7</v>
       </c>
       <c r="W16" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.07</v>
+        <v>3.65</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AE16" t="n">
         <v>1.84</v>
@@ -2388,10 +2388,10 @@
         <v>1.83</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.18</v>
+        <v>2.46</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46051.70833333334</v>
@@ -2403,27 +2403,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,76 +2444,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.82</v>
+        <v>3.68</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="N17" t="n">
-        <v>4.2</v>
+        <v>1.95</v>
       </c>
       <c r="O17" t="n">
-        <v>2.3</v>
+        <v>4.66</v>
       </c>
       <c r="P17" t="n">
-        <v>2.21</v>
+        <v>2.06</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.33</v>
+        <v>2.58</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S17" t="n">
-        <v>3.05</v>
+        <v>2.47</v>
       </c>
       <c r="T17" t="n">
-        <v>2.73</v>
+        <v>2.97</v>
       </c>
       <c r="U17" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="V17" t="n">
-        <v>6.3</v>
+        <v>7.6</v>
       </c>
       <c r="W17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.3</v>
+        <v>2.83</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.95</v>
+        <v>1.2</v>
       </c>
       <c r="AI17" s="3" t="n">
-        <v>46051.83333333334</v>
+        <v>46051.70833333334</v>
       </c>
     </row>
     <row r="18">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,61 +2563,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.58</v>
+        <v>1.82</v>
       </c>
       <c r="M18" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N18" t="n">
-        <v>2.85</v>
+        <v>3.75</v>
       </c>
       <c r="O18" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="P18" t="n">
-        <v>1.99</v>
+        <v>2.21</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.59</v>
+        <v>4.2</v>
       </c>
       <c r="R18" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>2.84</v>
+        <v>2.73</v>
       </c>
       <c r="T18" t="n">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="U18" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="V18" t="n">
-        <v>7.4</v>
+        <v>6.35</v>
       </c>
       <c r="W18" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X18" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.94</v>
+        <v>3.3</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.12</v>
+        <v>1.93</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.59</v>
+        <v>3.35</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE18" t="n">
         <v>1.75</v>
@@ -2626,12 +2626,131 @@
         <v>1.95</v>
       </c>
       <c r="AG18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AI18" s="3" t="n">
+        <v>46051.83333333334</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Botafogo</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Cruzeiro</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V19" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y19" t="n">
         <v>1.34</v>
       </c>
-      <c r="AH18" t="n">
+      <c r="Z19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH19" t="n">
         <v>1.5</v>
       </c>
-      <c r="AI18" s="3" t="n">
+      <c r="AI19" s="3" t="n">
         <v>46051.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2</v>
+        <v>2.49</v>
       </c>
       <c r="M13" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="N13" t="n">
-        <v>4.33</v>
+        <v>3.3</v>
       </c>
       <c r="O13" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="P13" t="n">
-        <v>1.95</v>
+        <v>1.59</v>
       </c>
       <c r="Q13" t="n">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="R13" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="S13" t="n">
-        <v>1.99</v>
+        <v>1.88</v>
       </c>
       <c r="T13" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="U13" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="V13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.12</v>
+        <v>1.87</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.55</v>
+        <v>6.75</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.37</v>
+        <v>1.54</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.64</v>
+        <v>1.49</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46051.625</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.49</v>
+        <v>2.1</v>
       </c>
       <c r="M14" t="n">
-        <v>2.5</v>
+        <v>3.35</v>
       </c>
       <c r="N14" t="n">
         <v>3.3</v>
       </c>
       <c r="O14" t="n">
-        <v>3.6</v>
+        <v>2.73</v>
       </c>
       <c r="P14" t="n">
-        <v>1.59</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.05</v>
+        <v>4.1</v>
       </c>
       <c r="R14" t="n">
-        <v>1.82</v>
+        <v>1.42</v>
       </c>
       <c r="S14" t="n">
-        <v>1.88</v>
+        <v>2.62</v>
       </c>
       <c r="T14" t="n">
-        <v>4.4</v>
+        <v>2.65</v>
       </c>
       <c r="U14" t="n">
-        <v>1.16</v>
+        <v>1.35</v>
       </c>
       <c r="V14" t="n">
-        <v>11</v>
+        <v>7.3</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.7</v>
+        <v>1.24</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.87</v>
+        <v>3.25</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.1</v>
+        <v>1.81</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.33</v>
+        <v>1.79</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.75</v>
+        <v>3</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.04</v>
+        <v>1.29</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.5</v>
+        <v>1.78</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.48</v>
+        <v>1.93</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.54</v>
+        <v>1.24</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.49</v>
+        <v>1.68</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46051.625</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
-        <v>3.35</v>
+        <v>2.88</v>
       </c>
       <c r="N15" t="n">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="O15" t="n">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>1.72</v>
       </c>
       <c r="S15" t="n">
-        <v>2.62</v>
+        <v>1.99</v>
       </c>
       <c r="T15" t="n">
-        <v>2.65</v>
+        <v>3.85</v>
       </c>
       <c r="U15" t="n">
-        <v>1.35</v>
+        <v>1.17</v>
       </c>
       <c r="V15" t="n">
-        <v>7.3</v>
+        <v>13</v>
       </c>
       <c r="W15" t="n">
         <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.24</v>
+        <v>1.64</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.25</v>
+        <v>2.12</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.81</v>
+        <v>2.83</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.79</v>
+        <v>1.37</v>
       </c>
       <c r="AC15" t="n">
-        <v>3</v>
+        <v>5.55</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.29</v>
+        <v>1.08</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.78</v>
+        <v>2.4</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.93</v>
+        <v>1.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46051.625</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2321,77 +2321,77 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L16" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O16" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="R16" t="n">
         <v>1.44</v>
       </c>
-      <c r="M16" t="n">
-        <v>4</v>
-      </c>
-      <c r="N16" t="n">
-        <v>6</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>6.38</v>
-      </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="U16" t="n">
         <v>1.31</v>
       </c>
-      <c r="S16" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.46</v>
-      </c>
       <c r="V16" t="n">
-        <v>5.7</v>
+        <v>7.6</v>
       </c>
       <c r="W16" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.2</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>2.46</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46051.70833333334</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2440,77 +2440,77 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.68</v>
+        <v>1.44</v>
       </c>
       <c r="M17" t="n">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="N17" t="n">
-        <v>1.95</v>
+        <v>6</v>
       </c>
       <c r="O17" t="n">
-        <v>4.66</v>
+        <v>1.79</v>
       </c>
       <c r="P17" t="n">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.58</v>
+        <v>6.38</v>
       </c>
       <c r="R17" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="S17" t="n">
-        <v>2.47</v>
+        <v>3.08</v>
       </c>
       <c r="T17" t="n">
-        <v>2.97</v>
+        <v>2.49</v>
       </c>
       <c r="U17" t="n">
-        <v>1.31</v>
+        <v>1.46</v>
       </c>
       <c r="V17" t="n">
-        <v>7.6</v>
+        <v>5.7</v>
       </c>
       <c r="W17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AD17" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z17" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AE17" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.2</v>
+        <v>2.46</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46051.70833333334</v>
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="M18" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="N18" t="n">
-        <v>3.75</v>
+        <v>4.36</v>
       </c>
       <c r="O18" t="n">
         <v>2.3</v>
@@ -2623,13 +2623,13 @@
         <v>1.75</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AG18" t="n">
         <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46051.83333333334</v>
@@ -2682,19 +2682,19 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.22</v>
+        <v>2.39</v>
       </c>
       <c r="M19" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="N19" t="n">
-        <v>2.87</v>
+        <v>2.82</v>
       </c>
       <c r="O19" t="n">
         <v>2.9</v>
       </c>
       <c r="P19" t="n">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="Q19" t="n">
         <v>3.3</v>
@@ -2724,19 +2724,19 @@
         <v>1.34</v>
       </c>
       <c r="Z19" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="AA19" t="n">
         <v>2.12</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AC19" t="n">
         <v>3.58</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE19" t="n">
         <v>1.75</v>

--- a/jogos_2026-01-29.xlsx
+++ b/jogos_2026-01-29.xlsx
@@ -662,31 +662,31 @@
         <v>2.5</v>
       </c>
       <c r="M2" t="n">
-        <v>2.72</v>
+        <v>2.69</v>
       </c>
       <c r="N2" t="n">
         <v>3</v>
       </c>
       <c r="O2" t="n">
-        <v>3.42</v>
+        <v>3.38</v>
       </c>
       <c r="P2" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.1</v>
+        <v>4.28</v>
       </c>
       <c r="R2" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="S2" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="T2" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="U2" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="V2" t="n">
         <v>9.9</v>
@@ -695,37 +695,37 @@
         <v>1.02</v>
       </c>
       <c r="X2" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AC2" t="n">
-        <v>6.85</v>
+        <v>6.55</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AG2" t="n">
         <v>1.36</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46051.375</v>
@@ -778,34 +778,34 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>5.35</v>
+        <v>6.03</v>
       </c>
       <c r="M3" t="n">
-        <v>3.75</v>
+        <v>3.73</v>
       </c>
       <c r="N3" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="O3" t="n">
-        <v>6.6</v>
+        <v>6.51</v>
       </c>
       <c r="P3" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q3" t="n">
         <v>2.1</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S3" t="n">
         <v>2.6</v>
       </c>
       <c r="T3" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="U3" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="V3" t="n">
         <v>6.7</v>
@@ -817,34 +817,34 @@
         <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AG3" t="n">
         <v>1.19</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46051.41666666666</v>
@@ -897,22 +897,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="M4" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N4" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="O4" t="n">
-        <v>4.45</v>
+        <v>4.88</v>
       </c>
       <c r="P4" t="n">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="R4" t="n">
         <v>1.31</v>
@@ -933,37 +933,37 @@
         <v>1.05</v>
       </c>
       <c r="X4" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.72</v>
+        <v>3.95</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.01</v>
+        <v>1.96</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.95</v>
+        <v>1.19</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46051.42708333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.2</v>
+        <v>5.25</v>
       </c>
       <c r="M6" t="n">
-        <v>2.6</v>
+        <v>4.65</v>
       </c>
       <c r="N6" t="n">
-        <v>2.58</v>
+        <v>1.5</v>
       </c>
       <c r="O6" t="n">
-        <v>4.45</v>
+        <v>4.55</v>
       </c>
       <c r="P6" t="n">
-        <v>1.66</v>
+        <v>2.75</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.75</v>
+        <v>1.89</v>
       </c>
       <c r="R6" t="n">
-        <v>1.74</v>
+        <v>1.17</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>4.05</v>
       </c>
       <c r="T6" t="n">
-        <v>3.85</v>
+        <v>2.04</v>
       </c>
       <c r="U6" t="n">
-        <v>1.14</v>
+        <v>1.73</v>
       </c>
       <c r="V6" t="n">
-        <v>11</v>
+        <v>4.1</v>
       </c>
       <c r="W6" t="n">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="X6" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.69</v>
+        <v>1.06</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.11</v>
+        <v>6.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.27</v>
+        <v>1.37</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.36</v>
+        <v>2.85</v>
       </c>
       <c r="AC6" t="n">
-        <v>6.5</v>
+        <v>1.94</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.05</v>
+        <v>1.77</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.36</v>
+        <v>1.46</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.5</v>
+        <v>2.57</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.5</v>
+        <v>1.12</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46051.5</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.78</v>
+        <v>3.05</v>
       </c>
       <c r="M7" t="n">
-        <v>4.5</v>
+        <v>2.75</v>
       </c>
       <c r="N7" t="n">
-        <v>1.48</v>
+        <v>2.75</v>
       </c>
       <c r="O7" t="n">
-        <v>4.35</v>
+        <v>4.06</v>
       </c>
       <c r="P7" t="n">
-        <v>2.76</v>
+        <v>1.66</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.89</v>
+        <v>3.78</v>
       </c>
       <c r="R7" t="n">
-        <v>1.17</v>
+        <v>1.73</v>
       </c>
       <c r="S7" t="n">
-        <v>4.05</v>
+        <v>2.07</v>
       </c>
       <c r="T7" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V7" t="n">
+        <v>11</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z7" t="n">
         <v>2.06</v>
       </c>
-      <c r="U7" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="V7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>6.4</v>
-      </c>
       <c r="AA7" t="n">
-        <v>1.4</v>
+        <v>3.28</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.85</v>
+        <v>1.28</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.94</v>
+        <v>6.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.83</v>
+        <v>1.05</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.4</v>
+        <v>2.35</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.6</v>
+        <v>1.55</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.13</v>
+        <v>1.35</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.11</v>
+        <v>1.32</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46051.5</v>
@@ -1373,28 +1373,28 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="M8" t="n">
         <v>3.2</v>
       </c>
       <c r="N8" t="n">
-        <v>3.7</v>
+        <v>4.56</v>
       </c>
       <c r="O8" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="P8" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.32</v>
+        <v>5.65</v>
       </c>
       <c r="R8" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="S8" t="n">
-        <v>2.47</v>
+        <v>2.39</v>
       </c>
       <c r="T8" t="n">
         <v>3.13</v>
@@ -1409,37 +1409,37 @@
         <v>1.04</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.78</v>
+        <v>2.73</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.84</v>
+        <v>3.75</v>
       </c>
       <c r="AD8" t="n">
         <v>1.18</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AG8" t="n">
         <v>1.26</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46051.52083333334</v>
@@ -1492,22 +1492,22 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="M9" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="N9" t="n">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="O9" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="P9" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.64</v>
+        <v>4.6</v>
       </c>
       <c r="R9" t="n">
         <v>1.27</v>
@@ -1516,7 +1516,7 @@
         <v>3.25</v>
       </c>
       <c r="T9" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="U9" t="n">
         <v>1.5</v>
@@ -1528,13 +1528,13 @@
         <v>1.09</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
         <v>1.15</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="AA9" t="n">
         <v>1.6</v>
@@ -1543,22 +1543,22 @@
         <v>2.19</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.28</v>
+        <v>2.46</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.97</v>
+        <v>2.09</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46051.54166666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="M11" t="n">
-        <v>3.68</v>
+        <v>3.51</v>
       </c>
       <c r="N11" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="O11" t="n">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="P11" t="n">
-        <v>2.57</v>
+        <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="R11" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="S11" t="n">
-        <v>3.58</v>
+        <v>2.88</v>
       </c>
       <c r="T11" t="n">
-        <v>2.15</v>
+        <v>2.65</v>
       </c>
       <c r="U11" t="n">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="V11" t="n">
-        <v>4.9</v>
+        <v>6.55</v>
       </c>
       <c r="W11" t="n">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.35</v>
+        <v>3.42</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.4</v>
+        <v>1.85</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.56</v>
+        <v>1.87</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.09</v>
+        <v>3.19</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.66</v>
+        <v>1.29</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.39</v>
+        <v>1.68</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.65</v>
+        <v>2.04</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.62</v>
+        <v>1.24</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46051.60416666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.4</v>
+        <v>2.92</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="N12" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="T12" t="n">
         <v>2.05</v>
       </c>
-      <c r="O12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.65</v>
-      </c>
       <c r="U12" t="n">
-        <v>1.42</v>
+        <v>1.65</v>
       </c>
       <c r="V12" t="n">
-        <v>6.55</v>
+        <v>4.7</v>
       </c>
       <c r="W12" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.42</v>
+        <v>5.82</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.95</v>
+        <v>2.56</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.04</v>
+        <v>2.09</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.34</v>
+        <v>1.66</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.68</v>
+        <v>1.38</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.27</v>
+        <v>1.65</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46051.60416666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.49</v>
+        <v>2.1</v>
       </c>
       <c r="M13" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="N13" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="O13" t="n">
-        <v>3.6</v>
+        <v>2.84</v>
       </c>
       <c r="P13" t="n">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.05</v>
+        <v>5.75</v>
       </c>
       <c r="R13" t="n">
-        <v>1.82</v>
+        <v>1.63</v>
       </c>
       <c r="S13" t="n">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="T13" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="U13" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="V13" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="W13" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.87</v>
+        <v>2.21</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AC13" t="n">
-        <v>6.75</v>
+        <v>5.99</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.54</v>
+        <v>1.36</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.49</v>
+        <v>1.65</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46051.625</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.1</v>
+        <v>2.58</v>
       </c>
       <c r="M14" t="n">
-        <v>3.35</v>
+        <v>2.5</v>
       </c>
       <c r="N14" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O14" t="n">
-        <v>2.73</v>
+        <v>3.64</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1</v>
+        <v>1.76</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.1</v>
+        <v>4.78</v>
       </c>
       <c r="R14" t="n">
-        <v>1.42</v>
+        <v>1.79</v>
       </c>
       <c r="S14" t="n">
-        <v>2.62</v>
+        <v>1.92</v>
       </c>
       <c r="T14" t="n">
-        <v>2.65</v>
+        <v>4.4</v>
       </c>
       <c r="U14" t="n">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="V14" t="n">
-        <v>7.3</v>
+        <v>15</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.24</v>
+        <v>1.68</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.25</v>
+        <v>2.15</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.81</v>
+        <v>3.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.79</v>
+        <v>1.33</v>
       </c>
       <c r="AC14" t="n">
-        <v>3</v>
+        <v>6.97</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.29</v>
+        <v>1.05</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.78</v>
+        <v>2.5</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.93</v>
+        <v>1.51</v>
       </c>
       <c r="AG14" t="n">
         <v>1.24</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46051.625</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="M15" t="n">
-        <v>2.88</v>
+        <v>3.31</v>
       </c>
       <c r="N15" t="n">
-        <v>4.33</v>
+        <v>3.3</v>
       </c>
       <c r="O15" t="n">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="P15" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="R15" t="n">
-        <v>1.72</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
-        <v>1.99</v>
+        <v>2.62</v>
       </c>
       <c r="T15" t="n">
-        <v>3.85</v>
+        <v>2.65</v>
       </c>
       <c r="U15" t="n">
-        <v>1.17</v>
+        <v>1.37</v>
       </c>
       <c r="V15" t="n">
-        <v>13</v>
+        <v>7.3</v>
       </c>
       <c r="W15" t="n">
         <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.64</v>
+        <v>1.24</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.12</v>
+        <v>3.25</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.83</v>
+        <v>1.81</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.37</v>
+        <v>1.79</v>
       </c>
       <c r="AC15" t="n">
-        <v>5.55</v>
+        <v>3</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.4</v>
+        <v>1.78</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.5</v>
+        <v>1.93</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46051.625</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.68</v>
+        <v>1.45</v>
       </c>
       <c r="M16" t="n">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="N16" t="n">
-        <v>1.95</v>
+        <v>6.16</v>
       </c>
       <c r="O16" t="n">
-        <v>4.66</v>
+        <v>1.97</v>
       </c>
       <c r="P16" t="n">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.58</v>
+        <v>6.21</v>
       </c>
       <c r="R16" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="S16" t="n">
-        <v>2.47</v>
+        <v>2.97</v>
       </c>
       <c r="T16" t="n">
-        <v>2.97</v>
+        <v>2.44</v>
       </c>
       <c r="U16" t="n">
-        <v>1.31</v>
+        <v>1.45</v>
       </c>
       <c r="V16" t="n">
-        <v>7.6</v>
+        <v>5.7</v>
       </c>
       <c r="W16" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.83</v>
+        <v>3.82</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.65</v>
+        <v>2.04</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.58</v>
+        <v>2.59</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.21</v>
+        <v>1.39</v>
       </c>
       <c r="AE16" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF16" t="n">
         <v>1.86</v>
       </c>
-      <c r="AF16" t="n">
-        <v>1.81</v>
-      </c>
       <c r="AG16" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.2</v>
+        <v>2.46</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46051.70833333334</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2440,77 +2440,77 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.44</v>
+        <v>3.68</v>
       </c>
       <c r="M17" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="N17" t="n">
-        <v>6</v>
+        <v>1.85</v>
       </c>
       <c r="O17" t="n">
-        <v>1.79</v>
+        <v>4.45</v>
       </c>
       <c r="P17" t="n">
-        <v>2.24</v>
+        <v>2.05</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.38</v>
+        <v>2.59</v>
       </c>
       <c r="R17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="U17" t="n">
         <v>1.31</v>
       </c>
-      <c r="S17" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.46</v>
-      </c>
       <c r="V17" t="n">
-        <v>5.7</v>
+        <v>7.6</v>
       </c>
       <c r="W17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AH17" t="n">
         <v>1.2</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>2.46</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46051.70833333334</v>
